--- a/excel-files/QUEZON CITY/SAN ANTONIO ES.xlsx
+++ b/excel-files/QUEZON CITY/SAN ANTONIO ES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10320"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BFDC8BA-CAC8-4FDA-87E4-8DECF37B149C}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DD6C8A3-06F6-FB42-8EA5-FEEF5F1B112D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -314,7 +314,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1729,8 +1729,10 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
@@ -1740,6 +1742,8 @@
         <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1766,7 +1770,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
@@ -1776,6 +1780,56 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
@@ -1805,14 +1859,9 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
@@ -1820,9 +1869,9 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
+        <top style="thin">
           <color rgb="FF000000"/>
-        </bottom>
+        </top>
       </border>
     </dxf>
     <dxf>
@@ -1843,16 +1892,17 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
         <name val="Bookman Old Style"/>
+        <family val="1"/>
         <charset val="134"/>
         <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFCAEDFB"/>
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2827,10 +2877,8 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
@@ -2840,8 +2888,6 @@
         <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2868,7 +2914,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
@@ -2878,63 +2924,6 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
@@ -2964,9 +2953,14 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
         <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
@@ -2974,9 +2968,9 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <top style="thin">
+        <bottom style="thin">
           <color rgb="FF000000"/>
-        </top>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2990,20 +2984,26 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <sz val="15"/>
+        <color rgb="FF000000"/>
         <name val="Bookman Old Style"/>
-        <family val="1"/>
         <charset val="134"/>
         <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="-0.499984740745262"/>
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFCAEDFB"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -3019,7 +3019,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="32" headerRowBorderDxfId="31" tableBorderDxfId="30">
   <autoFilter ref="A1:H145" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
@@ -3036,54 +3036,54 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
   <autoFilter ref="A2:AA127" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
-    <tableColumn id="2" xr3:uid="{C6CCCB1C-6639-4C28-A4BA-B187B2F73B59}" name="SUBJECTS" dataDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{945324E6-140A-476C-A8C3-23A16D4D262F}" name="Enrolment S.Y. 2025-2026 " dataDxfId="54"/>
-    <tableColumn id="4" xr3:uid="{A2D4C0AF-3699-4D3C-A791-2D7D8004CC89}" name="Quantity based on Target LAS - Q1 " dataDxfId="53">
+    <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{C6CCCB1C-6639-4C28-A4BA-B187B2F73B59}" name="SUBJECTS" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{945324E6-140A-476C-A8C3-23A16D4D262F}" name="Enrolment S.Y. 2025-2026 " dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{A2D4C0AF-3699-4D3C-A791-2D7D8004CC89}" name="Quantity based on Target LAS - Q1 " dataDxfId="23">
       <calculatedColumnFormula>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9CE2D7B1-8761-49A3-A313-E7834B16687D}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q1" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{FCD520AB-D938-4542-9B56-AEC07AB5F1DC}" name="Year of Delivery-LAS - Q1" dataDxfId="51"/>
-    <tableColumn id="7" xr3:uid="{674474DE-9D20-41C1-8261-DA9C4A95671C}" name="SOURCE - LAS (CO,RO, SDO) - Q1" dataDxfId="50"/>
-    <tableColumn id="8" xr3:uid="{58D9CB98-8F6F-4F61-9103-C27B8FFBDB51}" name="GAP - LAS - Q1" dataDxfId="49">
+    <tableColumn id="5" xr3:uid="{9CE2D7B1-8761-49A3-A313-E7834B16687D}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q1" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{FCD520AB-D938-4542-9B56-AEC07AB5F1DC}" name="Year of Delivery-LAS - Q1" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{674474DE-9D20-41C1-8261-DA9C4A95671C}" name="SOURCE - LAS (CO,RO, SDO) - Q1" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{58D9CB98-8F6F-4F61-9103-C27B8FFBDB51}" name="GAP - LAS - Q1" dataDxfId="19">
       <calculatedColumnFormula>IF((D3-E3)&lt;0,0,(D3-E3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E6406FC4-4491-4FD6-9EA2-F088E94C44F4}" name="SURPLUS - LAS - Q1" dataDxfId="48">
+    <tableColumn id="9" xr3:uid="{E6406FC4-4491-4FD6-9EA2-F088E94C44F4}" name="SURPLUS - LAS - Q1" dataDxfId="18">
       <calculatedColumnFormula>IF((E3-D3)&lt;0,0,(E3-D3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1E56D889-DC27-4BCB-B61E-06BBBE734949}" name="Quantity based on Target LAS - Q2" dataDxfId="47">
+    <tableColumn id="10" xr3:uid="{1E56D889-DC27-4BCB-B61E-06BBBE734949}" name="Quantity based on Target LAS - Q2" dataDxfId="17">
       <calculatedColumnFormula>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{E933BF99-834C-4F15-8181-7D005013BD85}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) Q2" dataDxfId="46"/>
-    <tableColumn id="12" xr3:uid="{F2E2CB95-E0BD-4C6E-ACFE-F201177004A0}" name="Year of Delivery-LAS Q2" dataDxfId="45"/>
-    <tableColumn id="13" xr3:uid="{163FBFFB-0AB7-44C8-89C4-72AA64C1EAC7}" name="SOURCE-LAS (CO,RO, SDO) Q2" dataDxfId="44"/>
-    <tableColumn id="14" xr3:uid="{EACC05A8-C68D-4495-BC08-73F093C4992F}" name="GAP - LAS -Q2" dataDxfId="43"/>
-    <tableColumn id="15" xr3:uid="{28A44E24-3E28-4B7F-BADE-28BB84F0B810}" name="SURPLUS - LAS -Q2" dataDxfId="42"/>
-    <tableColumn id="16" xr3:uid="{87878677-5715-46B6-9BA9-9D08DE9A3335}" name="Quantity based on Target LAS - Q3" dataDxfId="41">
+    <tableColumn id="11" xr3:uid="{E933BF99-834C-4F15-8181-7D005013BD85}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) Q2" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{F2E2CB95-E0BD-4C6E-ACFE-F201177004A0}" name="Year of Delivery-LAS Q2" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{163FBFFB-0AB7-44C8-89C4-72AA64C1EAC7}" name="SOURCE-LAS (CO,RO, SDO) Q2" dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{EACC05A8-C68D-4495-BC08-73F093C4992F}" name="GAP - LAS -Q2" dataDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{28A44E24-3E28-4B7F-BADE-28BB84F0B810}" name="SURPLUS - LAS -Q2" dataDxfId="12"/>
+    <tableColumn id="16" xr3:uid="{87878677-5715-46B6-9BA9-9D08DE9A3335}" name="Quantity based on Target LAS - Q3" dataDxfId="11">
       <calculatedColumnFormula>#REF!*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{48667A1F-77B1-47A6-83F7-61ED15F61DDB}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q3" dataDxfId="40"/>
-    <tableColumn id="18" xr3:uid="{56F2625D-2CEE-478E-A8DE-42A7191C3835}" name="Year of Delivery-LAS - Q3" dataDxfId="39"/>
-    <tableColumn id="19" xr3:uid="{EF0F614F-5FED-4639-8798-840D9677B8DA}" name="SOURCE-LAS (CO,RO, SDO) - Q3" dataDxfId="38"/>
-    <tableColumn id="20" xr3:uid="{FD91DDEE-DBA8-4E2C-94B2-23AE9F73CC4A}" name="GAP - LAS - Q3" dataDxfId="37">
+    <tableColumn id="17" xr3:uid="{48667A1F-77B1-47A6-83F7-61ED15F61DDB}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q3" dataDxfId="10"/>
+    <tableColumn id="18" xr3:uid="{56F2625D-2CEE-478E-A8DE-42A7191C3835}" name="Year of Delivery-LAS - Q3" dataDxfId="9"/>
+    <tableColumn id="19" xr3:uid="{EF0F614F-5FED-4639-8798-840D9677B8DA}" name="SOURCE-LAS (CO,RO, SDO) - Q3" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{FD91DDEE-DBA8-4E2C-94B2-23AE9F73CC4A}" name="GAP - LAS - Q3" dataDxfId="7">
       <calculatedColumnFormula>IF((P3-Q3)&lt;0,0,(P3-Q3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{DB598C6C-E489-4B0F-9BC6-B0981F7D2582}" name="SURPLUS - LAS - Q3" dataDxfId="36">
+    <tableColumn id="21" xr3:uid="{DB598C6C-E489-4B0F-9BC6-B0981F7D2582}" name="SURPLUS - LAS - Q3" dataDxfId="6">
       <calculatedColumnFormula>IF((Q3-P3)&lt;0,0,(Q3-P3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{8CD6906A-7980-46E8-80B2-8563AEBC71F7}" name="Quantity based on Target LAS - Q4" dataDxfId="35">
+    <tableColumn id="22" xr3:uid="{8CD6906A-7980-46E8-80B2-8563AEBC71F7}" name="Quantity based on Target LAS - Q4" dataDxfId="5">
       <calculatedColumnFormula>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{6287B1E4-D2AD-47C7-BD86-3391F339B1E3}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS)- Q4" dataDxfId="34"/>
-    <tableColumn id="24" xr3:uid="{205BCDBA-0424-492C-B4EF-841B8A3A1521}" name="Year of Delivery - LAS - Q4" dataDxfId="33"/>
-    <tableColumn id="25" xr3:uid="{8226E35B-1F3B-4D2A-815B-9D4C0A24EE7E}" name="SOURCE - LAS (CO,RO, SDO) - Q4" dataDxfId="32"/>
-    <tableColumn id="26" xr3:uid="{5B37A4B7-CD16-4D9A-8A47-D9EA73F613BC}" name="GAP - LAS - Q4" dataDxfId="31">
+    <tableColumn id="23" xr3:uid="{6287B1E4-D2AD-47C7-BD86-3391F339B1E3}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS)- Q4" dataDxfId="4"/>
+    <tableColumn id="24" xr3:uid="{205BCDBA-0424-492C-B4EF-841B8A3A1521}" name="Year of Delivery - LAS - Q4" dataDxfId="3"/>
+    <tableColumn id="25" xr3:uid="{8226E35B-1F3B-4D2A-815B-9D4C0A24EE7E}" name="SOURCE - LAS (CO,RO, SDO) - Q4" dataDxfId="2"/>
+    <tableColumn id="26" xr3:uid="{5B37A4B7-CD16-4D9A-8A47-D9EA73F613BC}" name="GAP - LAS - Q4" dataDxfId="1">
       <calculatedColumnFormula>IF((V3-W3)&lt;0,0,(V3-W3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{38E9C5F3-3FF5-4B13-A9DA-0081A90F35C5}" name="SURPLUS - LAS - Q4" dataDxfId="30">
+    <tableColumn id="27" xr3:uid="{38E9C5F3-3FF5-4B13-A9DA-0081A90F35C5}" name="SURPLUS - LAS - Q4" dataDxfId="0">
       <calculatedColumnFormula>IF((W3-V3)&lt;0,0,(W3-V3))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3092,54 +3092,54 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="61" headerRowBorderDxfId="62" tableBorderDxfId="60">
   <autoFilter ref="A2:AA140" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{73AEA048-228E-40E8-B07A-3A7C30BA0DC7}" name="SUBJECTS" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{187AF7E3-9651-4001-B779-AADEF0EAB05A}" name="Enrolment S.Y. 2025-2026 " dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{41F05D2B-5E6F-433A-B62B-2F1726EA10F2}" name="Quantity based on Target ADM-SLM - Q1 " dataDxfId="23">
+    <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{73AEA048-228E-40E8-B07A-3A7C30BA0DC7}" name="SUBJECTS" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{187AF7E3-9651-4001-B779-AADEF0EAB05A}" name="Enrolment S.Y. 2025-2026 " dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{41F05D2B-5E6F-433A-B62B-2F1726EA10F2}" name="Quantity based on Target ADM-SLM - Q1 " dataDxfId="56">
       <calculatedColumnFormula>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CDE5FD66-559D-4D0F-A587-312B6DC04A00}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q1" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{339CCB0D-A0D6-41EF-9023-6B8DF1A1D211}" name="Year of Delivery - ADM-SLM - Q1" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{66966C8F-6B7D-4027-80F0-10F5BEB94C36}" name="SOURCE - ADM-SLM (CO,RO, SDO) - Q1" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{F205DFF0-AD23-4608-82A0-E64C38A40A7F}" name="GAP - ADM-SLM - Q1" dataDxfId="19">
+    <tableColumn id="5" xr3:uid="{CDE5FD66-559D-4D0F-A587-312B6DC04A00}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q1" dataDxfId="55"/>
+    <tableColumn id="6" xr3:uid="{339CCB0D-A0D6-41EF-9023-6B8DF1A1D211}" name="Year of Delivery - ADM-SLM - Q1" dataDxfId="54"/>
+    <tableColumn id="7" xr3:uid="{66966C8F-6B7D-4027-80F0-10F5BEB94C36}" name="SOURCE - ADM-SLM (CO,RO, SDO) - Q1" dataDxfId="53"/>
+    <tableColumn id="8" xr3:uid="{F205DFF0-AD23-4608-82A0-E64C38A40A7F}" name="GAP - ADM-SLM - Q1" dataDxfId="52">
       <calculatedColumnFormula>IF((D3-E3)&lt;0,0,(D3-E3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{A97DBFEB-A833-47C5-A43D-C6E4D77683A6}" name="SURPLUS - ADM-SLM - Q1" dataDxfId="18">
+    <tableColumn id="9" xr3:uid="{A97DBFEB-A833-47C5-A43D-C6E4D77683A6}" name="SURPLUS - ADM-SLM - Q1" dataDxfId="51">
       <calculatedColumnFormula>IF((E3-D3)&lt;0,0,(E3-D3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{6A093D68-BC9F-46BB-AC8F-CA208309466C}" name="Quantity based on Target ADM-SLM - Q2" dataDxfId="17">
+    <tableColumn id="10" xr3:uid="{6A093D68-BC9F-46BB-AC8F-CA208309466C}" name="Quantity based on Target ADM-SLM - Q2" dataDxfId="50">
       <calculatedColumnFormula>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{CB914A26-115B-4765-A39C-5A2824E73671}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q2" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{35FFB32F-868E-4FBD-946A-0482CC3DE0D4}" name="Year of Delivery - ADM-SLM Q2" dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{987FB8ED-06DA-4311-80C5-DAF78B602129}" name="SOURCE - ADM-SLM (CO,RO, SDO) Q2" dataDxfId="14"/>
-    <tableColumn id="14" xr3:uid="{24CC35CF-2900-4C84-934F-7E29CCFCCEC9}" name="GAP - ADM-SLM - Q2" dataDxfId="13"/>
-    <tableColumn id="15" xr3:uid="{0DA82B8D-6A8D-469A-8302-7E7DD0B1BDC4}" name="SURPLUS - ADM-SLM -Q2" dataDxfId="12"/>
-    <tableColumn id="16" xr3:uid="{126A7F40-0CC3-4264-A57D-D7C0C9FE4720}" name="Quantity based on Target ADM-SLM - Q3" dataDxfId="11">
+    <tableColumn id="11" xr3:uid="{CB914A26-115B-4765-A39C-5A2824E73671}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q2" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{35FFB32F-868E-4FBD-946A-0482CC3DE0D4}" name="Year of Delivery - ADM-SLM Q2" dataDxfId="48"/>
+    <tableColumn id="13" xr3:uid="{987FB8ED-06DA-4311-80C5-DAF78B602129}" name="SOURCE - ADM-SLM (CO,RO, SDO) Q2" dataDxfId="47"/>
+    <tableColumn id="14" xr3:uid="{24CC35CF-2900-4C84-934F-7E29CCFCCEC9}" name="GAP - ADM-SLM - Q2" dataDxfId="46"/>
+    <tableColumn id="15" xr3:uid="{0DA82B8D-6A8D-469A-8302-7E7DD0B1BDC4}" name="SURPLUS - ADM-SLM -Q2" dataDxfId="45"/>
+    <tableColumn id="16" xr3:uid="{126A7F40-0CC3-4264-A57D-D7C0C9FE4720}" name="Quantity based on Target ADM-SLM - Q3" dataDxfId="44">
       <calculatedColumnFormula>#REF!*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{711B70A4-2160-43C1-900D-FD892755D7AB}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q3" dataDxfId="10"/>
-    <tableColumn id="18" xr3:uid="{D8C99A72-7FED-4E85-8CB4-4A08C56BCB15}" name="Year of Delivery - ADM-SLM - Q3" dataDxfId="9"/>
-    <tableColumn id="19" xr3:uid="{D48A881D-138B-4288-AA57-050C0AE3F5F6}" name="SOURCE - ADM-SLM(CO,RO, SDO) - Q3" dataDxfId="8"/>
-    <tableColumn id="20" xr3:uid="{B03A44EC-B25E-4D0D-B9E6-71825AC6E51F}" name="GAP - ADM-SLM - Q3" dataDxfId="7">
+    <tableColumn id="17" xr3:uid="{711B70A4-2160-43C1-900D-FD892755D7AB}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q3" dataDxfId="43"/>
+    <tableColumn id="18" xr3:uid="{D8C99A72-7FED-4E85-8CB4-4A08C56BCB15}" name="Year of Delivery - ADM-SLM - Q3" dataDxfId="42"/>
+    <tableColumn id="19" xr3:uid="{D48A881D-138B-4288-AA57-050C0AE3F5F6}" name="SOURCE - ADM-SLM(CO,RO, SDO) - Q3" dataDxfId="41"/>
+    <tableColumn id="20" xr3:uid="{B03A44EC-B25E-4D0D-B9E6-71825AC6E51F}" name="GAP - ADM-SLM - Q3" dataDxfId="40">
       <calculatedColumnFormula>IF((P3-Q3)&lt;0,0,(P3-Q3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{3338E724-88DC-45DA-8F55-7AAE5A560621}" name="SURPLUS - ADM-SLM - Q3" dataDxfId="6">
+    <tableColumn id="21" xr3:uid="{3338E724-88DC-45DA-8F55-7AAE5A560621}" name="SURPLUS - ADM-SLM - Q3" dataDxfId="39">
       <calculatedColumnFormula>IF((Q3-P3)&lt;0,0,(Q3-P3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{AC55FA3C-A61A-4AB0-8391-EC237845F1BF}" name="Quantity based on Target ADM-SLM - Q4" dataDxfId="5">
+    <tableColumn id="22" xr3:uid="{AC55FA3C-A61A-4AB0-8391-EC237845F1BF}" name="Quantity based on Target ADM-SLM - Q4" dataDxfId="38">
       <calculatedColumnFormula>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{D3F77FA4-2477-4BAF-A6FD-8446908907B9}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM)- Q4" dataDxfId="4"/>
-    <tableColumn id="24" xr3:uid="{C66CE0BE-6DCF-4E05-9DBD-D908450B3841}" name="Year of Delivery - ADM-SLM- Q4" dataDxfId="3"/>
-    <tableColumn id="25" xr3:uid="{AABA2263-B244-4CBF-87B1-CDAAECF763E4}" name="SOURCE - ADM-SLM - (CO,RO, SDO) - Q4" dataDxfId="2"/>
-    <tableColumn id="26" xr3:uid="{21E1F5D8-F09B-453A-90E6-AA7B2E8821D1}" name="GAP - ADM-SLM - Q4" dataDxfId="1">
+    <tableColumn id="23" xr3:uid="{D3F77FA4-2477-4BAF-A6FD-8446908907B9}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM)- Q4" dataDxfId="37"/>
+    <tableColumn id="24" xr3:uid="{C66CE0BE-6DCF-4E05-9DBD-D908450B3841}" name="Year of Delivery - ADM-SLM- Q4" dataDxfId="36"/>
+    <tableColumn id="25" xr3:uid="{AABA2263-B244-4CBF-87B1-CDAAECF763E4}" name="SOURCE - ADM-SLM - (CO,RO, SDO) - Q4" dataDxfId="35"/>
+    <tableColumn id="26" xr3:uid="{21E1F5D8-F09B-453A-90E6-AA7B2E8821D1}" name="GAP - ADM-SLM - Q4" dataDxfId="34">
       <calculatedColumnFormula>IF((V3-W3)&lt;0,0,(V3-W3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{67725D86-C1DE-4DB2-8FBD-99B8821906AB}" name="SURPLUS - ADM-SLM- Q4" dataDxfId="0">
+    <tableColumn id="27" xr3:uid="{67725D86-C1DE-4DB2-8FBD-99B8821906AB}" name="SURPLUS - ADM-SLM- Q4" dataDxfId="33">
       <calculatedColumnFormula>IF((W3-V3)&lt;0,0,(W3-V3))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3465,17 +3465,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H98"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="5" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.0859375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="5" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1015625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" customWidth="1"/>
     <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1">
+    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="42.75" customHeight="1">
+    <row r="2" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="29.25" customHeight="1">
+    <row r="3" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="21" customHeight="1">
+    <row r="4" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -3561,7 +3561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="25.5" customHeight="1">
+    <row r="5" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.149999999999999">
+    <row r="6" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3601,12 +3601,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="39.75" customHeight="1">
+    <row r="8" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -3626,7 +3626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="29.25" customHeight="1">
+    <row r="9" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" customHeight="1">
+    <row r="10" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -3666,7 +3666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="24" customHeight="1">
+    <row r="11" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19.149999999999999">
+    <row r="12" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3706,12 +3706,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="49.5" customHeight="1">
+    <row r="14" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -3731,7 +3731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="29.25" customHeight="1">
+    <row r="15" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>3</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="27" customHeight="1">
+    <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>3</v>
       </c>
@@ -3771,7 +3771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="23.25" customHeight="1">
+    <row r="17" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>3</v>
       </c>
@@ -3791,7 +3791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21" customHeight="1">
+    <row r="18" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>3</v>
       </c>
@@ -3811,7 +3811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.149999999999999">
+    <row r="19" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -3841,7 +3841,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="28.5" customHeight="1">
+    <row r="21" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>4</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="24" customHeight="1">
+    <row r="22" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>4</v>
       </c>
@@ -3881,7 +3881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="19.149999999999999">
+    <row r="23" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -3901,7 +3901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="27" customHeight="1">
+    <row r="24" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>4</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="33.75" customHeight="1">
+    <row r="25" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>4</v>
       </c>
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="33.75" customHeight="1">
+    <row r="26" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>4</v>
       </c>
@@ -3961,7 +3961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="33.75" customHeight="1">
+    <row r="27" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="27.75" customHeight="1">
+    <row r="28" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>4</v>
       </c>
@@ -4001,7 +4001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="27.75" customHeight="1">
+    <row r="29" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>4</v>
       </c>
@@ -4021,7 +4021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="27.75" customHeight="1">
+    <row r="30" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
@@ -4031,7 +4031,7 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" customHeight="1">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>5</v>
       </c>
@@ -4051,7 +4051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="27.75" customHeight="1">
+    <row r="32" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>5</v>
       </c>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="27.75" customHeight="1">
+    <row r="33" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>5</v>
       </c>
@@ -4091,7 +4091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="27.75" customHeight="1">
+    <row r="34" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>5</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="39" customHeight="1">
+    <row r="35" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>5</v>
       </c>
@@ -4131,7 +4131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="27.75" customHeight="1">
+    <row r="36" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>5</v>
       </c>
@@ -4151,7 +4151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="27.75" customHeight="1">
+    <row r="37" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>5</v>
       </c>
@@ -4171,7 +4171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="27.75" customHeight="1">
+    <row r="38" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>5</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="27.75" customHeight="1">
+    <row r="39" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>5</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="27.75" customHeight="1">
+    <row r="40" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
@@ -4221,7 +4221,7 @@
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" ht="27.75" customHeight="1">
+    <row r="41" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>6</v>
       </c>
@@ -4241,7 +4241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="27.75" customHeight="1">
+    <row r="42" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>6</v>
       </c>
@@ -4261,7 +4261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27.75" customHeight="1">
+    <row r="43" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>6</v>
       </c>
@@ -4281,7 +4281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="27.75" customHeight="1">
+    <row r="44" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>6</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="36.75" customHeight="1">
+    <row r="45" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>6</v>
       </c>
@@ -4321,7 +4321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="27.75" customHeight="1">
+    <row r="46" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>6</v>
       </c>
@@ -4341,7 +4341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="27.75" customHeight="1">
+    <row r="47" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>6</v>
       </c>
@@ -4361,7 +4361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="27.75" customHeight="1">
+    <row r="48" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>6</v>
       </c>
@@ -4381,7 +4381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.75" customHeight="1">
+    <row r="49" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>6</v>
       </c>
@@ -4401,7 +4401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="27.75" customHeight="1">
+    <row r="50" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
@@ -4411,7 +4411,7 @@
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" ht="27.75" customHeight="1">
+    <row r="51" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10">
         <v>7</v>
       </c>
@@ -4431,7 +4431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="27.75" customHeight="1">
+    <row r="52" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10">
         <v>7</v>
       </c>
@@ -4451,7 +4451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="27.75" customHeight="1">
+    <row r="53" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10">
         <v>7</v>
       </c>
@@ -4471,7 +4471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="27.75" customHeight="1">
+    <row r="54" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
         <v>7</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="39" customHeight="1">
+    <row r="55" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10">
         <v>7</v>
       </c>
@@ -4511,7 +4511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="27.75" customHeight="1">
+    <row r="56" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="10">
         <v>7</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="27.75" customHeight="1">
+    <row r="57" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="10">
         <v>7</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="27.75" customHeight="1">
+    <row r="58" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="10">
         <v>7</v>
       </c>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="27.75" customHeight="1">
+    <row r="59" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="10">
         <v>7</v>
       </c>
@@ -4591,7 +4591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="27.75" customHeight="1">
+    <row r="60" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
@@ -4601,7 +4601,7 @@
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" ht="27.75" customHeight="1">
+    <row r="61" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="10">
         <v>8</v>
       </c>
@@ -4621,7 +4621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="27.75" customHeight="1">
+    <row r="62" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="10">
         <v>8</v>
       </c>
@@ -4641,7 +4641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="27.75" customHeight="1">
+    <row r="63" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>8</v>
       </c>
@@ -4661,7 +4661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="27.75" customHeight="1">
+    <row r="64" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>8</v>
       </c>
@@ -4681,7 +4681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="27.75" customHeight="1">
+    <row r="65" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>8</v>
       </c>
@@ -4701,7 +4701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="27.75" customHeight="1">
+    <row r="66" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>8</v>
       </c>
@@ -4721,7 +4721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="27.75" customHeight="1">
+    <row r="67" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>8</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="27.75" customHeight="1">
+    <row r="68" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>8</v>
       </c>
@@ -4761,7 +4761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="27.75" customHeight="1">
+    <row r="69" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>8</v>
       </c>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="27.75" customHeight="1">
+    <row r="70" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
@@ -4791,7 +4791,7 @@
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" ht="27.75" customHeight="1">
+    <row r="71" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>9</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="27.75" customHeight="1">
+    <row r="72" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>9</v>
       </c>
@@ -4831,7 +4831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="27.75" customHeight="1">
+    <row r="73" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>9</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="27.75" customHeight="1">
+    <row r="74" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>9</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="27.75" customHeight="1">
+    <row r="75" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>9</v>
       </c>
@@ -4891,7 +4891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="27.75" customHeight="1">
+    <row r="76" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>9</v>
       </c>
@@ -4911,7 +4911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="27.75" customHeight="1">
+    <row r="77" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>9</v>
       </c>
@@ -4931,7 +4931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="27.75" customHeight="1">
+    <row r="78" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>9</v>
       </c>
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="27.75" customHeight="1">
+    <row r="79" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>9</v>
       </c>
@@ -4971,7 +4971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="27.75" customHeight="1">
+    <row r="80" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="7"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -4981,7 +4981,7 @@
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" ht="27.75" customHeight="1">
+    <row r="81" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>10</v>
       </c>
@@ -5001,7 +5001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="27.75" customHeight="1">
+    <row r="82" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>10</v>
       </c>
@@ -5021,7 +5021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="27.75" customHeight="1">
+    <row r="83" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>10</v>
       </c>
@@ -5041,7 +5041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="27.75" customHeight="1">
+    <row r="84" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>10</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="27.75" customHeight="1">
+    <row r="85" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>10</v>
       </c>
@@ -5081,7 +5081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="27.75" customHeight="1">
+    <row r="86" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>10</v>
       </c>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="27.75" customHeight="1">
+    <row r="87" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>10</v>
       </c>
@@ -5121,7 +5121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="27.75" customHeight="1">
+    <row r="88" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>10</v>
       </c>
@@ -5141,7 +5141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="27.75" customHeight="1">
+    <row r="89" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>10</v>
       </c>
@@ -5161,7 +5161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="27.75" customHeight="1">
+    <row r="90" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
@@ -5171,7 +5171,7 @@
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8" ht="39.75" customHeight="1">
+    <row r="91" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>23</v>
       </c>
@@ -5191,7 +5191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="27.75" customHeight="1">
+    <row r="92" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>23</v>
       </c>
@@ -5211,7 +5211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="27.75" customHeight="1">
+    <row r="93" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>23</v>
       </c>
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="27.75" customHeight="1">
+    <row r="94" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>23</v>
       </c>
@@ -5251,7 +5251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="40.5" customHeight="1">
+    <row r="95" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>23</v>
       </c>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="38.25" customHeight="1">
+    <row r="96" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>23</v>
       </c>
@@ -5291,7 +5291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="27.75" customHeight="1">
+    <row r="97" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>23</v>
       </c>
@@ -5311,7 +5311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="47.25" customHeight="1">
+    <row r="98" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>23</v>
       </c>
@@ -5338,8 +5338,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5354,36 +5354,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <dimension ref="A1:AA127"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="35.5703125" customWidth="1"/>
-    <col min="12" max="12" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="31.5703125" customWidth="1"/>
-    <col min="14" max="15" width="20.85546875" customWidth="1"/>
-    <col min="16" max="16" width="21.5703125" customWidth="1"/>
-    <col min="17" max="17" width="33.42578125" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="32.85546875" customWidth="1"/>
-    <col min="20" max="21" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.4140625" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="26.09765625" customWidth="1"/>
+    <col min="5" max="5" width="23.13671875" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5625" customWidth="1"/>
+    <col min="8" max="9" width="20.84765625" customWidth="1"/>
+    <col min="10" max="10" width="13.71875" customWidth="1"/>
+    <col min="11" max="11" width="35.51171875" customWidth="1"/>
+    <col min="12" max="12" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.609375" customWidth="1"/>
+    <col min="14" max="15" width="20.84765625" customWidth="1"/>
+    <col min="16" max="16" width="21.5234375" customWidth="1"/>
+    <col min="17" max="17" width="33.359375" customWidth="1"/>
+    <col min="18" max="18" width="25.828125" customWidth="1"/>
+    <col min="19" max="19" width="32.8203125" customWidth="1"/>
+    <col min="20" max="21" width="20.84765625" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="23" max="23" width="25.01953125" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" customWidth="1"/>
+    <col min="25" max="25" width="20.84765625" customWidth="1"/>
+    <col min="26" max="26" width="14.796875" customWidth="1"/>
+    <col min="27" max="27" width="15.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="42" t="s">
         <v>32</v>
       </c>
@@ -5417,7 +5417,7 @@
       <c r="Z1" s="45"/>
       <c r="AA1" s="45"/>
     </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -5500,22 +5500,24 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="30.6" customHeight="1">
+    <row r="3" spans="1:27" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
         <v>60</v>
       </c>
       <c r="B3" s="33"/>
-      <c r="C3" s="32"/>
+      <c r="C3" s="32">
+        <v>318</v>
+      </c>
       <c r="D3" s="34">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2544</v>
       </c>
       <c r="E3" s="34"/>
       <c r="F3" s="32"/>
       <c r="G3" s="34"/>
       <c r="H3" s="34">
         <f>IF((D3-E3)&lt;0,0,(D3-E3))</f>
-        <v>0</v>
+        <v>2544</v>
       </c>
       <c r="I3" s="34">
         <f>IF((E3-D3)&lt;0,0,(E3-D3))</f>
@@ -5523,14 +5525,14 @@
       </c>
       <c r="J3" s="34">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2544</v>
       </c>
       <c r="K3" s="34"/>
       <c r="L3" s="32"/>
       <c r="M3" s="34"/>
       <c r="N3" s="5">
         <f t="shared" ref="N3" si="0">IF((J3-K3)&lt;0,0,(J3-K3))</f>
-        <v>0</v>
+        <v>2544</v>
       </c>
       <c r="O3" s="5">
         <f t="shared" ref="O3" si="1">IF((K3-J3)&lt;0,0,(K3-J3))</f>
@@ -5538,14 +5540,14 @@
       </c>
       <c r="P3" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2544</v>
       </c>
       <c r="Q3" s="34"/>
       <c r="R3" s="32"/>
       <c r="S3" s="34"/>
       <c r="T3" s="34">
         <f>IF((P3-Q3)&lt;0,0,(P3-Q3))</f>
-        <v>0</v>
+        <v>2544</v>
       </c>
       <c r="U3" s="34">
         <f>IF((Q3-P3)&lt;0,0,(Q3-P3))</f>
@@ -5553,21 +5555,21 @@
       </c>
       <c r="V3" s="34">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2544</v>
       </c>
       <c r="W3" s="34"/>
       <c r="X3" s="32"/>
       <c r="Y3" s="34"/>
       <c r="Z3" s="34">
         <f>IF((V3-W3)&lt;0,0,(V3-W3))</f>
-        <v>0</v>
+        <v>2544</v>
       </c>
       <c r="AA3" s="34">
         <f>IF((W3-V3)&lt;0,0,(W3-V3))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="4" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
@@ -5579,24 +5581,26 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1">
+        <v>317</v>
+      </c>
       <c r="D5" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="1"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5">
         <f t="shared" ref="H5:H77" si="2">IF((D5-E5)&lt;0,0,(D5-E5))</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I77" si="3">IF((E5-D5)&lt;0,0,(E5-D5))</f>
@@ -5604,14 +5608,14 @@
       </c>
       <c r="J5" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="1"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5">
         <f t="shared" ref="N5" si="4">IF((J5-K5)&lt;0,0,(J5-K5))</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="O5" s="5">
         <f t="shared" ref="O5" si="5">IF((K5-J5)&lt;0,0,(K5-J5))</f>
@@ -5619,14 +5623,14 @@
       </c>
       <c r="P5" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="Q5" s="5"/>
       <c r="R5" s="1"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5">
         <f t="shared" ref="T5" si="6">IF((P5-Q5)&lt;0,0,(P5-Q5))</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" ref="U5" si="7">IF((Q5-P5)&lt;0,0,(Q5-P5))</f>
@@ -5634,38 +5638,40 @@
       </c>
       <c r="V5" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="W5" s="5"/>
       <c r="X5" s="1"/>
       <c r="Y5" s="5"/>
       <c r="Z5" s="5">
         <f t="shared" ref="Z5" si="8">IF((V5-W5)&lt;0,0,(V5-W5))</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="AA5" s="5">
         <f t="shared" ref="AA5" si="9">IF((W5-V5)&lt;0,0,(W5-V5))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="1">
+        <v>317</v>
+      </c>
       <c r="D6" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="1"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="3"/>
@@ -5673,14 +5679,14 @@
       </c>
       <c r="J6" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="1"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5">
         <f t="shared" ref="N6:N69" si="10">IF((J6-K6)&lt;0,0,(J6-K6))</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="O6" s="5">
         <f t="shared" ref="O6:O69" si="11">IF((K6-J6)&lt;0,0,(K6-J6))</f>
@@ -5688,14 +5694,14 @@
       </c>
       <c r="P6" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="Q6" s="5"/>
       <c r="R6" s="1"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5">
         <f t="shared" ref="T6:T69" si="12">IF((P6-Q6)&lt;0,0,(P6-Q6))</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" ref="U6:U69" si="13">IF((Q6-P6)&lt;0,0,(Q6-P6))</f>
@@ -5703,38 +5709,40 @@
       </c>
       <c r="V6" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="W6" s="5"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="5"/>
       <c r="Z6" s="5">
         <f t="shared" ref="Z6:Z69" si="14">IF((V6-W6)&lt;0,0,(V6-W6))</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="AA6" s="5">
         <f t="shared" ref="AA6:AA69" si="15">IF((W6-V6)&lt;0,0,(W6-V6))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="1"/>
+      <c r="C7" s="1">
+        <v>317</v>
+      </c>
       <c r="D7" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="1"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="3"/>
@@ -5742,14 +5750,14 @@
       </c>
       <c r="J7" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="1"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="O7" s="5">
         <f t="shared" si="11"/>
@@ -5757,14 +5765,14 @@
       </c>
       <c r="P7" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="1"/>
       <c r="S7" s="5"/>
       <c r="T7" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="13"/>
@@ -5772,38 +5780,40 @@
       </c>
       <c r="V7" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="W7" s="5"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="AA7" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="1">
+        <v>317</v>
+      </c>
       <c r="D8" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="1"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="3"/>
@@ -5811,14 +5821,14 @@
       </c>
       <c r="J8" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="1"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="O8" s="5">
         <f t="shared" si="11"/>
@@ -5826,14 +5836,14 @@
       </c>
       <c r="P8" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="1"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="13"/>
@@ -5841,38 +5851,40 @@
       </c>
       <c r="V8" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="W8" s="5"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="AA8" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="1"/>
+      <c r="C9" s="1">
+        <v>317</v>
+      </c>
       <c r="D9" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="1"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="3"/>
@@ -5880,14 +5892,14 @@
       </c>
       <c r="J9" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="1"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="O9" s="5">
         <f t="shared" si="11"/>
@@ -5895,14 +5907,14 @@
       </c>
       <c r="P9" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="Q9" s="5"/>
       <c r="R9" s="1"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="13"/>
@@ -5910,38 +5922,40 @@
       </c>
       <c r="V9" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="W9" s="5"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="AA9" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1">
+        <v>317</v>
+      </c>
       <c r="D10" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="1"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5">
         <f>IF((D10-E10)&lt;0,0,(D10-E10))</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="I10" s="5">
         <f>IF((E10-D10)&lt;0,0,(E10-D10))</f>
@@ -5949,14 +5963,14 @@
       </c>
       <c r="J10" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="1"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="O10" s="5">
         <f t="shared" si="11"/>
@@ -5964,14 +5978,14 @@
       </c>
       <c r="P10" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="Q10" s="5"/>
       <c r="R10" s="1"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="13"/>
@@ -5979,38 +5993,40 @@
       </c>
       <c r="V10" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="W10" s="5"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="AA10" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="1"/>
+      <c r="C11" s="1">
+        <v>317</v>
+      </c>
       <c r="D11" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="1"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5">
         <f>IF((D11-E11)&lt;0,0,(D11-E11))</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="I11" s="5">
         <f>IF((E11-D11)&lt;0,0,(E11-D11))</f>
@@ -6018,14 +6034,14 @@
       </c>
       <c r="J11" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="1"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="O11" s="5">
         <f t="shared" si="11"/>
@@ -6033,14 +6049,14 @@
       </c>
       <c r="P11" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="Q11" s="5"/>
       <c r="R11" s="1"/>
       <c r="S11" s="5"/>
       <c r="T11" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="13"/>
@@ -6048,38 +6064,40 @@
       </c>
       <c r="V11" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="W11" s="5"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="5"/>
       <c r="Z11" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>1</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="1">
+        <v>317</v>
+      </c>
       <c r="D12" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="1"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5">
         <f>IF((D12-E12)&lt;0,0,(D12-E12))</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="I12" s="5">
         <f>IF((E12-D12)&lt;0,0,(E12-D12))</f>
@@ -6087,14 +6105,14 @@
       </c>
       <c r="J12" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="1"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="O12" s="5">
         <f t="shared" si="11"/>
@@ -6102,14 +6120,14 @@
       </c>
       <c r="P12" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="Q12" s="5"/>
       <c r="R12" s="1"/>
       <c r="S12" s="5"/>
       <c r="T12" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="U12" s="5">
         <f t="shared" si="13"/>
@@ -6117,21 +6135,21 @@
       </c>
       <c r="V12" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="W12" s="5"/>
       <c r="X12" s="1"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2536</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6144,24 +6162,26 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="1"/>
+      <c r="C14" s="1">
+        <v>348</v>
+      </c>
       <c r="D14" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="1"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="3"/>
@@ -6169,14 +6189,14 @@
       </c>
       <c r="J14" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="K14" s="5"/>
       <c r="L14" s="1"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="O14" s="5">
         <f t="shared" si="11"/>
@@ -6184,14 +6204,14 @@
       </c>
       <c r="P14" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="Q14" s="5"/>
       <c r="R14" s="1"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="U14" s="5">
         <f t="shared" si="13"/>
@@ -6199,38 +6219,40 @@
       </c>
       <c r="V14" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="W14" s="5"/>
       <c r="X14" s="1"/>
       <c r="Y14" s="5"/>
       <c r="Z14" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="1"/>
+      <c r="C15" s="1">
+        <v>348</v>
+      </c>
       <c r="D15" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="1"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="3"/>
@@ -6238,14 +6260,14 @@
       </c>
       <c r="J15" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="1"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="O15" s="5">
         <f t="shared" si="11"/>
@@ -6253,14 +6275,14 @@
       </c>
       <c r="P15" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="Q15" s="5"/>
       <c r="R15" s="1"/>
       <c r="S15" s="5"/>
       <c r="T15" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="U15" s="5">
         <f t="shared" si="13"/>
@@ -6268,38 +6290,40 @@
       </c>
       <c r="V15" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="W15" s="5"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="5"/>
       <c r="Z15" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="AA15" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="1"/>
+      <c r="C16" s="1">
+        <v>348</v>
+      </c>
       <c r="D16" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="1"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="3"/>
@@ -6307,14 +6331,14 @@
       </c>
       <c r="J16" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="K16" s="5"/>
       <c r="L16" s="1"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="O16" s="5">
         <f t="shared" si="11"/>
@@ -6322,14 +6346,14 @@
       </c>
       <c r="P16" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="Q16" s="5"/>
       <c r="R16" s="1"/>
       <c r="S16" s="5"/>
       <c r="T16" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="U16" s="5">
         <f t="shared" si="13"/>
@@ -6337,38 +6361,40 @@
       </c>
       <c r="V16" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="W16" s="5"/>
       <c r="X16" s="1"/>
       <c r="Y16" s="5"/>
       <c r="Z16" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="1"/>
+      <c r="C17" s="1">
+        <v>348</v>
+      </c>
       <c r="D17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="1"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="3"/>
@@ -6376,14 +6402,14 @@
       </c>
       <c r="J17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="K17" s="5"/>
       <c r="L17" s="1"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="O17" s="5">
         <f t="shared" si="11"/>
@@ -6391,14 +6417,14 @@
       </c>
       <c r="P17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="Q17" s="5"/>
       <c r="R17" s="1"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="U17" s="5">
         <f t="shared" si="13"/>
@@ -6406,38 +6432,40 @@
       </c>
       <c r="V17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="W17" s="5"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="1"/>
+      <c r="C18" s="1">
+        <v>348</v>
+      </c>
       <c r="D18" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="1"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="3"/>
@@ -6445,14 +6473,14 @@
       </c>
       <c r="J18" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="K18" s="5"/>
       <c r="L18" s="1"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="O18" s="5">
         <f t="shared" si="11"/>
@@ -6460,14 +6488,14 @@
       </c>
       <c r="P18" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="Q18" s="5"/>
       <c r="R18" s="1"/>
       <c r="S18" s="5"/>
       <c r="T18" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="U18" s="5">
         <f t="shared" si="13"/>
@@ -6475,38 +6503,40 @@
       </c>
       <c r="V18" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="W18" s="5"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="5"/>
       <c r="Z18" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="1"/>
+      <c r="C19" s="1">
+        <v>348</v>
+      </c>
       <c r="D19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="1"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5">
         <f>IF((D19-E19)&lt;0,0,(D19-E19))</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="I19" s="5">
         <f>IF((E19-D19)&lt;0,0,(E19-D19))</f>
@@ -6514,14 +6544,14 @@
       </c>
       <c r="J19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="K19" s="5"/>
       <c r="L19" s="1"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="O19" s="5">
         <f t="shared" si="11"/>
@@ -6529,14 +6559,14 @@
       </c>
       <c r="P19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="Q19" s="5"/>
       <c r="R19" s="1"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="U19" s="5">
         <f t="shared" si="13"/>
@@ -6544,38 +6574,40 @@
       </c>
       <c r="V19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="W19" s="5"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>2</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="1"/>
+      <c r="C20" s="1">
+        <v>348</v>
+      </c>
       <c r="D20" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="1"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5">
         <f>IF((D20-E20)&lt;0,0,(D20-E20))</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="I20" s="5">
         <f>IF((E20-D20)&lt;0,0,(E20-D20))</f>
@@ -6583,14 +6615,14 @@
       </c>
       <c r="J20" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="K20" s="5"/>
       <c r="L20" s="1"/>
       <c r="M20" s="5"/>
       <c r="N20" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="O20" s="5">
         <f t="shared" si="11"/>
@@ -6598,14 +6630,14 @@
       </c>
       <c r="P20" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="Q20" s="5"/>
       <c r="R20" s="1"/>
       <c r="S20" s="5"/>
       <c r="T20" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="U20" s="5">
         <f t="shared" si="13"/>
@@ -6613,38 +6645,40 @@
       </c>
       <c r="V20" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="W20" s="5"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="5"/>
       <c r="Z20" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="AA20" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>2</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="1"/>
+      <c r="C21" s="1">
+        <v>348</v>
+      </c>
       <c r="D21" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="1"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5">
         <f>IF((D21-E21)&lt;0,0,(D21-E21))</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="I21" s="5">
         <f>IF((E21-D21)&lt;0,0,(E21-D21))</f>
@@ -6652,14 +6686,14 @@
       </c>
       <c r="J21" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="1"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="O21" s="5">
         <f t="shared" si="11"/>
@@ -6667,14 +6701,14 @@
       </c>
       <c r="P21" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="Q21" s="5"/>
       <c r="R21" s="1"/>
       <c r="S21" s="5"/>
       <c r="T21" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="U21" s="5">
         <f t="shared" si="13"/>
@@ -6682,21 +6716,21 @@
       </c>
       <c r="V21" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="W21" s="5"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="5"/>
       <c r="Z21" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -6710,24 +6744,26 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="1"/>
+      <c r="C23" s="1">
+        <v>378</v>
+      </c>
       <c r="D23" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="1"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="3"/>
@@ -6735,14 +6771,14 @@
       </c>
       <c r="J23" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="K23" s="5"/>
       <c r="L23" s="1"/>
       <c r="M23" s="5"/>
       <c r="N23" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="O23" s="5">
         <f t="shared" si="11"/>
@@ -6750,14 +6786,14 @@
       </c>
       <c r="P23" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="Q23" s="5"/>
       <c r="R23" s="1"/>
       <c r="S23" s="5"/>
       <c r="T23" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="U23" s="5">
         <f t="shared" si="13"/>
@@ -6765,38 +6801,40 @@
       </c>
       <c r="V23" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="W23" s="5"/>
       <c r="X23" s="1"/>
       <c r="Y23" s="5"/>
       <c r="Z23" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="AA23" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="1"/>
+      <c r="C24" s="1">
+        <v>378</v>
+      </c>
       <c r="D24" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="1"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="3"/>
@@ -6804,14 +6842,14 @@
       </c>
       <c r="J24" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="K24" s="5"/>
       <c r="L24" s="1"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="O24" s="5">
         <f t="shared" si="11"/>
@@ -6819,14 +6857,14 @@
       </c>
       <c r="P24" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="Q24" s="5"/>
       <c r="R24" s="1"/>
       <c r="S24" s="5"/>
       <c r="T24" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="U24" s="5">
         <f t="shared" si="13"/>
@@ -6834,38 +6872,40 @@
       </c>
       <c r="V24" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="W24" s="5"/>
       <c r="X24" s="1"/>
       <c r="Y24" s="5"/>
       <c r="Z24" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="AA24" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="1"/>
+      <c r="C25" s="1">
+        <v>378</v>
+      </c>
       <c r="D25" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="1"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="3"/>
@@ -6873,14 +6913,14 @@
       </c>
       <c r="J25" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="K25" s="5"/>
       <c r="L25" s="1"/>
       <c r="M25" s="5"/>
       <c r="N25" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="O25" s="5">
         <f t="shared" si="11"/>
@@ -6888,14 +6928,14 @@
       </c>
       <c r="P25" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="Q25" s="5"/>
       <c r="R25" s="1"/>
       <c r="S25" s="5"/>
       <c r="T25" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="U25" s="5">
         <f t="shared" si="13"/>
@@ -6903,38 +6943,40 @@
       </c>
       <c r="V25" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="W25" s="5"/>
       <c r="X25" s="1"/>
       <c r="Y25" s="5"/>
       <c r="Z25" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="1"/>
+      <c r="C26" s="1">
+        <v>378</v>
+      </c>
       <c r="D26" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="1"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="3"/>
@@ -6942,14 +6984,14 @@
       </c>
       <c r="J26" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="K26" s="5"/>
       <c r="L26" s="1"/>
       <c r="M26" s="5"/>
       <c r="N26" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="O26" s="5">
         <f t="shared" si="11"/>
@@ -6957,14 +6999,14 @@
       </c>
       <c r="P26" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="Q26" s="5"/>
       <c r="R26" s="1"/>
       <c r="S26" s="5"/>
       <c r="T26" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="U26" s="5">
         <f t="shared" si="13"/>
@@ -6972,38 +7014,40 @@
       </c>
       <c r="V26" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="W26" s="5"/>
       <c r="X26" s="1"/>
       <c r="Y26" s="5"/>
       <c r="Z26" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="AA26" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="1"/>
+      <c r="C27" s="1">
+        <v>378</v>
+      </c>
       <c r="D27" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="1"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="3"/>
@@ -7011,14 +7055,14 @@
       </c>
       <c r="J27" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="K27" s="5"/>
       <c r="L27" s="1"/>
       <c r="M27" s="5"/>
       <c r="N27" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="O27" s="5">
         <f t="shared" si="11"/>
@@ -7026,14 +7070,14 @@
       </c>
       <c r="P27" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="Q27" s="5"/>
       <c r="R27" s="1"/>
       <c r="S27" s="5"/>
       <c r="T27" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="U27" s="5">
         <f t="shared" si="13"/>
@@ -7041,38 +7085,40 @@
       </c>
       <c r="V27" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="W27" s="5"/>
       <c r="X27" s="1"/>
       <c r="Y27" s="5"/>
       <c r="Z27" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="1"/>
+      <c r="C28" s="1">
+        <v>378</v>
+      </c>
       <c r="D28" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="1"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="3"/>
@@ -7080,14 +7126,14 @@
       </c>
       <c r="J28" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="K28" s="5"/>
       <c r="L28" s="1"/>
       <c r="M28" s="5"/>
       <c r="N28" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="O28" s="5">
         <f t="shared" si="11"/>
@@ -7095,14 +7141,14 @@
       </c>
       <c r="P28" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="Q28" s="5"/>
       <c r="R28" s="1"/>
       <c r="S28" s="5"/>
       <c r="T28" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="U28" s="5">
         <f t="shared" si="13"/>
@@ -7110,38 +7156,40 @@
       </c>
       <c r="V28" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="W28" s="5"/>
       <c r="X28" s="1"/>
       <c r="Y28" s="5"/>
       <c r="Z28" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="AA28" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="1"/>
+      <c r="C29" s="1">
+        <v>378</v>
+      </c>
       <c r="D29" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="1"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5">
         <f>IF((D29-E29)&lt;0,0,(D29-E29))</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="I29" s="5">
         <f>IF((E29-D29)&lt;0,0,(E29-D29))</f>
@@ -7149,14 +7197,14 @@
       </c>
       <c r="J29" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="K29" s="5"/>
       <c r="L29" s="1"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="O29" s="5">
         <f t="shared" si="11"/>
@@ -7164,14 +7212,14 @@
       </c>
       <c r="P29" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="Q29" s="5"/>
       <c r="R29" s="1"/>
       <c r="S29" s="5"/>
       <c r="T29" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="U29" s="5">
         <f t="shared" si="13"/>
@@ -7179,38 +7227,40 @@
       </c>
       <c r="V29" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="W29" s="5"/>
       <c r="X29" s="1"/>
       <c r="Y29" s="5"/>
       <c r="Z29" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="AA29" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>3</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="1"/>
+      <c r="C30" s="1">
+        <v>378</v>
+      </c>
       <c r="D30" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="1"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5">
         <f>IF((D30-E30)&lt;0,0,(D30-E30))</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="I30" s="5">
         <f>IF((E30-D30)&lt;0,0,(E30-D30))</f>
@@ -7218,14 +7268,14 @@
       </c>
       <c r="J30" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="K30" s="5"/>
       <c r="L30" s="1"/>
       <c r="M30" s="5"/>
       <c r="N30" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="O30" s="5">
         <f t="shared" si="11"/>
@@ -7233,14 +7283,14 @@
       </c>
       <c r="P30" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="Q30" s="5"/>
       <c r="R30" s="1"/>
       <c r="S30" s="5"/>
       <c r="T30" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="U30" s="5">
         <f t="shared" si="13"/>
@@ -7248,38 +7298,40 @@
       </c>
       <c r="V30" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="W30" s="5"/>
       <c r="X30" s="1"/>
       <c r="Y30" s="5"/>
       <c r="Z30" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="AA30" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>3</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="1"/>
+      <c r="C31" s="1">
+        <v>378</v>
+      </c>
       <c r="D31" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="1"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5">
         <f>IF((D31-E31)&lt;0,0,(D31-E31))</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="I31" s="5">
         <f>IF((E31-D31)&lt;0,0,(E31-D31))</f>
@@ -7287,14 +7339,14 @@
       </c>
       <c r="J31" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="K31" s="5"/>
       <c r="L31" s="1"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="O31" s="5">
         <f t="shared" si="11"/>
@@ -7302,14 +7354,14 @@
       </c>
       <c r="P31" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="Q31" s="5"/>
       <c r="R31" s="1"/>
       <c r="S31" s="5"/>
       <c r="T31" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="U31" s="5">
         <f t="shared" si="13"/>
@@ -7317,21 +7369,21 @@
       </c>
       <c r="V31" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="W31" s="5"/>
       <c r="X31" s="1"/>
       <c r="Y31" s="5"/>
       <c r="Z31" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="AA31" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7345,24 +7397,26 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="1"/>
+      <c r="C33" s="1">
+        <v>428</v>
+      </c>
       <c r="D33" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="1"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="3"/>
@@ -7370,14 +7424,14 @@
       </c>
       <c r="J33" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="K33" s="5"/>
       <c r="L33" s="1"/>
       <c r="M33" s="5"/>
       <c r="N33" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="O33" s="5">
         <f t="shared" si="11"/>
@@ -7385,14 +7439,14 @@
       </c>
       <c r="P33" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="Q33" s="5"/>
       <c r="R33" s="1"/>
       <c r="S33" s="5"/>
       <c r="T33" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="U33" s="5">
         <f t="shared" si="13"/>
@@ -7400,38 +7454,40 @@
       </c>
       <c r="V33" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="W33" s="5"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="5"/>
       <c r="Z33" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="AA33" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C34" s="1"/>
+      <c r="C34" s="1">
+        <v>428</v>
+      </c>
       <c r="D34" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="1"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="3"/>
@@ -7439,14 +7495,14 @@
       </c>
       <c r="J34" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="K34" s="5"/>
       <c r="L34" s="1"/>
       <c r="M34" s="5"/>
       <c r="N34" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="O34" s="5">
         <f t="shared" si="11"/>
@@ -7454,14 +7510,14 @@
       </c>
       <c r="P34" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="Q34" s="5"/>
       <c r="R34" s="1"/>
       <c r="S34" s="5"/>
       <c r="T34" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="U34" s="5">
         <f t="shared" si="13"/>
@@ -7469,38 +7525,40 @@
       </c>
       <c r="V34" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="W34" s="5"/>
       <c r="X34" s="1"/>
       <c r="Y34" s="5"/>
       <c r="Z34" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="AA34" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="1"/>
+      <c r="C35" s="1">
+        <v>428</v>
+      </c>
       <c r="D35" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="1"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="3"/>
@@ -7508,14 +7566,14 @@
       </c>
       <c r="J35" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="K35" s="5"/>
       <c r="L35" s="1"/>
       <c r="M35" s="5"/>
       <c r="N35" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="O35" s="5">
         <f t="shared" si="11"/>
@@ -7523,14 +7581,14 @@
       </c>
       <c r="P35" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="Q35" s="5"/>
       <c r="R35" s="1"/>
       <c r="S35" s="5"/>
       <c r="T35" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="U35" s="5">
         <f t="shared" si="13"/>
@@ -7538,38 +7596,40 @@
       </c>
       <c r="V35" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="W35" s="5"/>
       <c r="X35" s="1"/>
       <c r="Y35" s="5"/>
       <c r="Z35" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="AA35" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C36" s="1"/>
+      <c r="C36" s="1">
+        <v>428</v>
+      </c>
       <c r="D36" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="1"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="3"/>
@@ -7577,14 +7637,14 @@
       </c>
       <c r="J36" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="K36" s="5"/>
       <c r="L36" s="1"/>
       <c r="M36" s="5"/>
       <c r="N36" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="O36" s="5">
         <f t="shared" si="11"/>
@@ -7592,14 +7652,14 @@
       </c>
       <c r="P36" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="Q36" s="5"/>
       <c r="R36" s="1"/>
       <c r="S36" s="5"/>
       <c r="T36" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="U36" s="5">
         <f t="shared" si="13"/>
@@ -7607,38 +7667,40 @@
       </c>
       <c r="V36" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="W36" s="5"/>
       <c r="X36" s="1"/>
       <c r="Y36" s="5"/>
       <c r="Z36" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="AA36" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="1"/>
+      <c r="C37" s="1">
+        <v>428</v>
+      </c>
       <c r="D37" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="1"/>
       <c r="G37" s="5"/>
       <c r="H37" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="3"/>
@@ -7646,14 +7708,14 @@
       </c>
       <c r="J37" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="K37" s="5"/>
       <c r="L37" s="1"/>
       <c r="M37" s="5"/>
       <c r="N37" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="O37" s="5">
         <f t="shared" si="11"/>
@@ -7661,14 +7723,14 @@
       </c>
       <c r="P37" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="Q37" s="5"/>
       <c r="R37" s="1"/>
       <c r="S37" s="5"/>
       <c r="T37" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="U37" s="5">
         <f t="shared" si="13"/>
@@ -7676,38 +7738,40 @@
       </c>
       <c r="V37" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="W37" s="5"/>
       <c r="X37" s="1"/>
       <c r="Y37" s="5"/>
       <c r="Z37" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="AA37" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C38" s="1"/>
+      <c r="C38" s="1">
+        <v>428</v>
+      </c>
       <c r="D38" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="1"/>
       <c r="G38" s="5"/>
       <c r="H38" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="3"/>
@@ -7715,14 +7779,14 @@
       </c>
       <c r="J38" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="K38" s="5"/>
       <c r="L38" s="1"/>
       <c r="M38" s="5"/>
       <c r="N38" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="O38" s="5">
         <f t="shared" si="11"/>
@@ -7730,14 +7794,14 @@
       </c>
       <c r="P38" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="Q38" s="5"/>
       <c r="R38" s="1"/>
       <c r="S38" s="5"/>
       <c r="T38" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="U38" s="5">
         <f t="shared" si="13"/>
@@ -7745,38 +7809,40 @@
       </c>
       <c r="V38" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="W38" s="5"/>
       <c r="X38" s="1"/>
       <c r="Y38" s="5"/>
       <c r="Z38" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="AA38" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C39" s="1"/>
+      <c r="C39" s="1">
+        <v>428</v>
+      </c>
       <c r="D39" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="1"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="3"/>
@@ -7784,14 +7850,14 @@
       </c>
       <c r="J39" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="K39" s="5"/>
       <c r="L39" s="1"/>
       <c r="M39" s="5"/>
       <c r="N39" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="O39" s="5">
         <f t="shared" si="11"/>
@@ -7799,14 +7865,14 @@
       </c>
       <c r="P39" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="Q39" s="5"/>
       <c r="R39" s="1"/>
       <c r="S39" s="5"/>
       <c r="T39" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="U39" s="5">
         <f t="shared" si="13"/>
@@ -7814,38 +7880,40 @@
       </c>
       <c r="V39" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="W39" s="5"/>
       <c r="X39" s="1"/>
       <c r="Y39" s="5"/>
       <c r="Z39" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="AA39" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="1"/>
+      <c r="C40" s="1">
+        <v>428</v>
+      </c>
       <c r="D40" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="1"/>
       <c r="G40" s="5"/>
       <c r="H40" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="I40" s="5">
         <f t="shared" si="3"/>
@@ -7853,14 +7921,14 @@
       </c>
       <c r="J40" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="K40" s="5"/>
       <c r="L40" s="1"/>
       <c r="M40" s="5"/>
       <c r="N40" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="O40" s="5">
         <f t="shared" si="11"/>
@@ -7868,14 +7936,14 @@
       </c>
       <c r="P40" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="Q40" s="5"/>
       <c r="R40" s="1"/>
       <c r="S40" s="5"/>
       <c r="T40" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="U40" s="5">
         <f t="shared" si="13"/>
@@ -7883,38 +7951,40 @@
       </c>
       <c r="V40" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="W40" s="5"/>
       <c r="X40" s="1"/>
       <c r="Y40" s="5"/>
       <c r="Z40" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="AA40" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C41" s="1"/>
+      <c r="C41" s="1">
+        <v>428</v>
+      </c>
       <c r="D41" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="1"/>
       <c r="G41" s="5"/>
       <c r="H41" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="I41" s="5">
         <f t="shared" si="3"/>
@@ -7922,14 +7992,14 @@
       </c>
       <c r="J41" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="K41" s="5"/>
       <c r="L41" s="1"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="O41" s="5">
         <f t="shared" si="11"/>
@@ -7937,14 +8007,14 @@
       </c>
       <c r="P41" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="Q41" s="5"/>
       <c r="R41" s="1"/>
       <c r="S41" s="5"/>
       <c r="T41" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="U41" s="5">
         <f t="shared" si="13"/>
@@ -7952,21 +8022,21 @@
       </c>
       <c r="V41" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="W41" s="5"/>
       <c r="X41" s="1"/>
       <c r="Y41" s="5"/>
       <c r="Z41" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="AA41" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -7980,24 +8050,26 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C43" s="1"/>
+      <c r="C43" s="1">
+        <v>312</v>
+      </c>
       <c r="D43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="1"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="I43" s="5">
         <f t="shared" si="3"/>
@@ -8005,14 +8077,14 @@
       </c>
       <c r="J43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="K43" s="5"/>
       <c r="L43" s="1"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="O43" s="5">
         <f t="shared" si="11"/>
@@ -8020,14 +8092,14 @@
       </c>
       <c r="P43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="Q43" s="5"/>
       <c r="R43" s="1"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="U43" s="5">
         <f t="shared" si="13"/>
@@ -8035,38 +8107,40 @@
       </c>
       <c r="V43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="W43" s="5"/>
       <c r="X43" s="1"/>
       <c r="Y43" s="5"/>
       <c r="Z43" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="AA43" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C44" s="1"/>
+      <c r="C44" s="1">
+        <v>312</v>
+      </c>
       <c r="D44" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="1"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="I44" s="5">
         <f t="shared" si="3"/>
@@ -8074,14 +8148,14 @@
       </c>
       <c r="J44" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="K44" s="5"/>
       <c r="L44" s="1"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="O44" s="5">
         <f t="shared" si="11"/>
@@ -8089,14 +8163,14 @@
       </c>
       <c r="P44" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="Q44" s="5"/>
       <c r="R44" s="1"/>
       <c r="S44" s="5"/>
       <c r="T44" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="U44" s="5">
         <f t="shared" si="13"/>
@@ -8104,38 +8178,40 @@
       </c>
       <c r="V44" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="W44" s="5"/>
       <c r="X44" s="1"/>
       <c r="Y44" s="5"/>
       <c r="Z44" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C45" s="1"/>
+      <c r="C45" s="1">
+        <v>312</v>
+      </c>
       <c r="D45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="1"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="I45" s="5">
         <f t="shared" si="3"/>
@@ -8143,14 +8219,14 @@
       </c>
       <c r="J45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="K45" s="5"/>
       <c r="L45" s="1"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="O45" s="5">
         <f t="shared" si="11"/>
@@ -8158,14 +8234,14 @@
       </c>
       <c r="P45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="Q45" s="5"/>
       <c r="R45" s="1"/>
       <c r="S45" s="5"/>
       <c r="T45" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="U45" s="5">
         <f t="shared" si="13"/>
@@ -8173,38 +8249,40 @@
       </c>
       <c r="V45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="W45" s="5"/>
       <c r="X45" s="1"/>
       <c r="Y45" s="5"/>
       <c r="Z45" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C46" s="1"/>
+      <c r="C46" s="1">
+        <v>312</v>
+      </c>
       <c r="D46" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="1"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="3"/>
@@ -8212,14 +8290,14 @@
       </c>
       <c r="J46" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="K46" s="5"/>
       <c r="L46" s="1"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="O46" s="5">
         <f t="shared" si="11"/>
@@ -8227,14 +8305,14 @@
       </c>
       <c r="P46" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="Q46" s="5"/>
       <c r="R46" s="1"/>
       <c r="S46" s="5"/>
       <c r="T46" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="U46" s="5">
         <f t="shared" si="13"/>
@@ -8242,38 +8320,40 @@
       </c>
       <c r="V46" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="W46" s="5"/>
       <c r="X46" s="1"/>
       <c r="Y46" s="5"/>
       <c r="Z46" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="AA46" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C47" s="1"/>
+      <c r="C47" s="1">
+        <v>312</v>
+      </c>
       <c r="D47" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="1"/>
       <c r="G47" s="5"/>
       <c r="H47" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="I47" s="5">
         <f t="shared" si="3"/>
@@ -8281,14 +8361,14 @@
       </c>
       <c r="J47" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="K47" s="5"/>
       <c r="L47" s="1"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="O47" s="5">
         <f t="shared" si="11"/>
@@ -8296,14 +8376,14 @@
       </c>
       <c r="P47" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="Q47" s="5"/>
       <c r="R47" s="1"/>
       <c r="S47" s="5"/>
       <c r="T47" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="U47" s="5">
         <f t="shared" si="13"/>
@@ -8311,38 +8391,40 @@
       </c>
       <c r="V47" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="W47" s="5"/>
       <c r="X47" s="1"/>
       <c r="Y47" s="5"/>
       <c r="Z47" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="AA47" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C48" s="1"/>
+      <c r="C48" s="1">
+        <v>312</v>
+      </c>
       <c r="D48" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="1"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="I48" s="5">
         <f t="shared" si="3"/>
@@ -8350,14 +8432,14 @@
       </c>
       <c r="J48" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="K48" s="5"/>
       <c r="L48" s="1"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="O48" s="5">
         <f t="shared" si="11"/>
@@ -8365,14 +8447,14 @@
       </c>
       <c r="P48" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="Q48" s="5"/>
       <c r="R48" s="1"/>
       <c r="S48" s="5"/>
       <c r="T48" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="U48" s="5">
         <f t="shared" si="13"/>
@@ -8380,38 +8462,40 @@
       </c>
       <c r="V48" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="W48" s="5"/>
       <c r="X48" s="1"/>
       <c r="Y48" s="5"/>
       <c r="Z48" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="AA48" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C49" s="1"/>
+      <c r="C49" s="1">
+        <v>312</v>
+      </c>
       <c r="D49" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="1"/>
       <c r="G49" s="5"/>
       <c r="H49" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="3"/>
@@ -8419,14 +8503,14 @@
       </c>
       <c r="J49" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="K49" s="5"/>
       <c r="L49" s="1"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="O49" s="5">
         <f t="shared" si="11"/>
@@ -8434,14 +8518,14 @@
       </c>
       <c r="P49" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="Q49" s="5"/>
       <c r="R49" s="1"/>
       <c r="S49" s="5"/>
       <c r="T49" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="U49" s="5">
         <f t="shared" si="13"/>
@@ -8449,38 +8533,40 @@
       </c>
       <c r="V49" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="W49" s="5"/>
       <c r="X49" s="1"/>
       <c r="Y49" s="5"/>
       <c r="Z49" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="AA49" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="1"/>
+      <c r="C50" s="1">
+        <v>312</v>
+      </c>
       <c r="D50" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="1"/>
       <c r="G50" s="5"/>
       <c r="H50" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="I50" s="5">
         <f t="shared" si="3"/>
@@ -8488,14 +8574,14 @@
       </c>
       <c r="J50" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="K50" s="5"/>
       <c r="L50" s="1"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="O50" s="5">
         <f t="shared" si="11"/>
@@ -8503,14 +8589,14 @@
       </c>
       <c r="P50" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="Q50" s="5"/>
       <c r="R50" s="1"/>
       <c r="S50" s="5"/>
       <c r="T50" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="U50" s="5">
         <f t="shared" si="13"/>
@@ -8518,38 +8604,40 @@
       </c>
       <c r="V50" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="W50" s="5"/>
       <c r="X50" s="1"/>
       <c r="Y50" s="5"/>
       <c r="Z50" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="AA50" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C51" s="1"/>
+      <c r="C51" s="1">
+        <v>312</v>
+      </c>
       <c r="D51" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="1"/>
       <c r="G51" s="5"/>
       <c r="H51" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="I51" s="5">
         <f t="shared" si="3"/>
@@ -8557,14 +8645,14 @@
       </c>
       <c r="J51" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="K51" s="5"/>
       <c r="L51" s="1"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="O51" s="5">
         <f t="shared" si="11"/>
@@ -8572,14 +8660,14 @@
       </c>
       <c r="P51" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="Q51" s="5"/>
       <c r="R51" s="1"/>
       <c r="S51" s="5"/>
       <c r="T51" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="U51" s="5">
         <f t="shared" si="13"/>
@@ -8587,21 +8675,21 @@
       </c>
       <c r="V51" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="W51" s="5"/>
       <c r="X51" s="1"/>
       <c r="Y51" s="5"/>
       <c r="Z51" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="AA51" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8615,24 +8703,26 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>6</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C53" s="1"/>
+      <c r="C53" s="1">
+        <v>344</v>
+      </c>
       <c r="D53" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="1"/>
       <c r="G53" s="5"/>
       <c r="H53" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="I53" s="5">
         <f t="shared" si="3"/>
@@ -8640,14 +8730,14 @@
       </c>
       <c r="J53" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="K53" s="5"/>
       <c r="L53" s="1"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="O53" s="5">
         <f t="shared" si="11"/>
@@ -8655,14 +8745,14 @@
       </c>
       <c r="P53" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="Q53" s="5"/>
       <c r="R53" s="1"/>
       <c r="S53" s="5"/>
       <c r="T53" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="U53" s="5">
         <f t="shared" si="13"/>
@@ -8670,38 +8760,40 @@
       </c>
       <c r="V53" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="W53" s="5"/>
       <c r="X53" s="1"/>
       <c r="Y53" s="5"/>
       <c r="Z53" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="AA53" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>6</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C54" s="1"/>
+      <c r="C54" s="1">
+        <v>344</v>
+      </c>
       <c r="D54" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="1"/>
       <c r="G54" s="5"/>
       <c r="H54" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="I54" s="5">
         <f t="shared" si="3"/>
@@ -8709,14 +8801,14 @@
       </c>
       <c r="J54" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="K54" s="5"/>
       <c r="L54" s="1"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="O54" s="5">
         <f t="shared" si="11"/>
@@ -8724,14 +8816,14 @@
       </c>
       <c r="P54" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="Q54" s="5"/>
       <c r="R54" s="1"/>
       <c r="S54" s="5"/>
       <c r="T54" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="U54" s="5">
         <f t="shared" si="13"/>
@@ -8739,38 +8831,40 @@
       </c>
       <c r="V54" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="W54" s="5"/>
       <c r="X54" s="1"/>
       <c r="Y54" s="5"/>
       <c r="Z54" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="AA54" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C55" s="1"/>
+      <c r="C55" s="1">
+        <v>344</v>
+      </c>
       <c r="D55" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="E55" s="5"/>
       <c r="F55" s="1"/>
       <c r="G55" s="5"/>
       <c r="H55" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="I55" s="5">
         <f t="shared" si="3"/>
@@ -8778,14 +8872,14 @@
       </c>
       <c r="J55" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="K55" s="5"/>
       <c r="L55" s="1"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="O55" s="5">
         <f t="shared" si="11"/>
@@ -8793,14 +8887,14 @@
       </c>
       <c r="P55" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="Q55" s="5"/>
       <c r="R55" s="1"/>
       <c r="S55" s="5"/>
       <c r="T55" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="U55" s="5">
         <f t="shared" si="13"/>
@@ -8808,38 +8902,40 @@
       </c>
       <c r="V55" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="W55" s="5"/>
       <c r="X55" s="1"/>
       <c r="Y55" s="5"/>
       <c r="Z55" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="AA55" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C56" s="1"/>
+      <c r="C56" s="1">
+        <v>344</v>
+      </c>
       <c r="D56" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="1"/>
       <c r="G56" s="5"/>
       <c r="H56" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="I56" s="5">
         <f t="shared" si="3"/>
@@ -8847,14 +8943,14 @@
       </c>
       <c r="J56" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="K56" s="5"/>
       <c r="L56" s="1"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="O56" s="5">
         <f t="shared" si="11"/>
@@ -8862,14 +8958,14 @@
       </c>
       <c r="P56" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="Q56" s="5"/>
       <c r="R56" s="1"/>
       <c r="S56" s="5"/>
       <c r="T56" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="U56" s="5">
         <f t="shared" si="13"/>
@@ -8877,38 +8973,40 @@
       </c>
       <c r="V56" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="W56" s="5"/>
       <c r="X56" s="1"/>
       <c r="Y56" s="5"/>
       <c r="Z56" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="AA56" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C57" s="1"/>
+      <c r="C57" s="1">
+        <v>344</v>
+      </c>
       <c r="D57" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="1"/>
       <c r="G57" s="5"/>
       <c r="H57" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="I57" s="5">
         <f t="shared" si="3"/>
@@ -8916,14 +9014,14 @@
       </c>
       <c r="J57" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="K57" s="5"/>
       <c r="L57" s="1"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="O57" s="5">
         <f t="shared" si="11"/>
@@ -8931,14 +9029,14 @@
       </c>
       <c r="P57" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="Q57" s="5"/>
       <c r="R57" s="1"/>
       <c r="S57" s="5"/>
       <c r="T57" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="U57" s="5">
         <f t="shared" si="13"/>
@@ -8946,38 +9044,40 @@
       </c>
       <c r="V57" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="W57" s="5"/>
       <c r="X57" s="1"/>
       <c r="Y57" s="5"/>
       <c r="Z57" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="AA57" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C58" s="1"/>
+      <c r="C58" s="1">
+        <v>344</v>
+      </c>
       <c r="D58" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="E58" s="5"/>
       <c r="F58" s="1"/>
       <c r="G58" s="5"/>
       <c r="H58" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="I58" s="5">
         <f t="shared" si="3"/>
@@ -8985,14 +9085,14 @@
       </c>
       <c r="J58" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="K58" s="5"/>
       <c r="L58" s="1"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="11"/>
@@ -9000,14 +9100,14 @@
       </c>
       <c r="P58" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="Q58" s="5"/>
       <c r="R58" s="1"/>
       <c r="S58" s="5"/>
       <c r="T58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="U58" s="5">
         <f t="shared" si="13"/>
@@ -9015,38 +9115,40 @@
       </c>
       <c r="V58" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="W58" s="5"/>
       <c r="X58" s="1"/>
       <c r="Y58" s="5"/>
       <c r="Z58" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="AA58" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
       <c r="B59" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C59" s="1"/>
+      <c r="C59" s="1">
+        <v>344</v>
+      </c>
       <c r="D59" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="1"/>
       <c r="G59" s="5"/>
       <c r="H59" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="I59" s="5">
         <f t="shared" si="3"/>
@@ -9054,14 +9156,14 @@
       </c>
       <c r="J59" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="K59" s="5"/>
       <c r="L59" s="1"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="O59" s="5">
         <f t="shared" si="11"/>
@@ -9069,14 +9171,14 @@
       </c>
       <c r="P59" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="Q59" s="5"/>
       <c r="R59" s="1"/>
       <c r="S59" s="5"/>
       <c r="T59" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="U59" s="5">
         <f t="shared" si="13"/>
@@ -9084,38 +9186,40 @@
       </c>
       <c r="V59" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="W59" s="5"/>
       <c r="X59" s="1"/>
       <c r="Y59" s="5"/>
       <c r="Z59" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="AA59" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C60" s="1"/>
+      <c r="C60" s="1">
+        <v>344</v>
+      </c>
       <c r="D60" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="1"/>
       <c r="G60" s="5"/>
       <c r="H60" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="I60" s="5">
         <f t="shared" si="3"/>
@@ -9123,14 +9227,14 @@
       </c>
       <c r="J60" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="K60" s="5"/>
       <c r="L60" s="1"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="O60" s="5">
         <f t="shared" si="11"/>
@@ -9138,14 +9242,14 @@
       </c>
       <c r="P60" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="Q60" s="5"/>
       <c r="R60" s="1"/>
       <c r="S60" s="5"/>
       <c r="T60" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="U60" s="5">
         <f t="shared" si="13"/>
@@ -9153,38 +9257,40 @@
       </c>
       <c r="V60" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="W60" s="5"/>
       <c r="X60" s="1"/>
       <c r="Y60" s="5"/>
       <c r="Z60" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="AA60" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C61" s="1"/>
+      <c r="C61" s="1">
+        <v>344</v>
+      </c>
       <c r="D61" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="1"/>
       <c r="G61" s="5"/>
       <c r="H61" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="I61" s="5">
         <f t="shared" si="3"/>
@@ -9192,14 +9298,14 @@
       </c>
       <c r="J61" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="K61" s="5"/>
       <c r="L61" s="1"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="O61" s="5">
         <f t="shared" si="11"/>
@@ -9207,14 +9313,14 @@
       </c>
       <c r="P61" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="Q61" s="5"/>
       <c r="R61" s="1"/>
       <c r="S61" s="5"/>
       <c r="T61" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="U61" s="5">
         <f t="shared" si="13"/>
@@ -9222,21 +9328,21 @@
       </c>
       <c r="V61" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="W61" s="5"/>
       <c r="X61" s="1"/>
       <c r="Y61" s="5"/>
       <c r="Z61" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2752</v>
       </c>
       <c r="AA61" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -9250,7 +9356,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9319,7 +9425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9388,7 +9494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9457,7 +9563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9526,7 +9632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9595,7 +9701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -9664,7 +9770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -9733,7 +9839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -9802,7 +9908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -9871,7 +9977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -9885,7 +9991,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -9954,7 +10060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10023,7 +10129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10092,7 +10198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10161,7 +10267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10230,7 +10336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10299,7 +10405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10368,7 +10474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10437,7 +10543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10506,7 +10612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10520,7 +10626,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10589,7 +10695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -10658,7 +10764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -10727,7 +10833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -10796,7 +10902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -10865,7 +10971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -10934,7 +11040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11003,7 +11109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11072,7 +11178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11141,7 +11247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11155,7 +11261,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11224,7 +11330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11293,7 +11399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11362,7 +11468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11431,7 +11537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11500,7 +11606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11569,7 +11675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -11638,7 +11744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -11707,7 +11813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -11776,7 +11882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -11790,7 +11896,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    <row r="103" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>23</v>
       </c>
@@ -11859,7 +11965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>23</v>
       </c>
@@ -11928,7 +12034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>23</v>
       </c>
@@ -11997,7 +12103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>23</v>
       </c>
@@ -12066,7 +12172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>23</v>
       </c>
@@ -12135,7 +12241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>23</v>
       </c>
@@ -12204,7 +12310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
+    <row r="109" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>23</v>
       </c>
@@ -12273,7 +12379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>23</v>
       </c>
@@ -12342,7 +12448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12353,7 +12459,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12415,7 +12521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12477,7 +12583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -12539,7 +12645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -12601,7 +12707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -12663,7 +12769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -12725,7 +12831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -12787,7 +12893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -12849,7 +12955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -12911,7 +13017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -12973,7 +13079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13035,7 +13141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13097,7 +13203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13159,7 +13265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13221,7 +13327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13283,7 +13389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -13342,189 +13448,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
+    <protectedRange sqref="C2:C3 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61" name="Textbooks"/>
     <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
   </protectedRanges>
@@ -13539,8 +13465,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -13558,35 +13484,35 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <dimension ref="A1:AB140"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="24.42578125" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" customWidth="1"/>
-    <col min="13" max="15" width="20.85546875" customWidth="1"/>
-    <col min="16" max="16" width="21.5703125" customWidth="1"/>
-    <col min="17" max="17" width="29.140625" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="32.85546875" customWidth="1"/>
-    <col min="20" max="21" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.4140625" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="16.41015625" customWidth="1"/>
+    <col min="5" max="5" width="23.13671875" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5625" customWidth="1"/>
+    <col min="8" max="9" width="20.84765625" customWidth="1"/>
+    <col min="10" max="10" width="13.71875" customWidth="1"/>
+    <col min="11" max="11" width="24.48046875" customWidth="1"/>
+    <col min="12" max="12" width="18.16015625" customWidth="1"/>
+    <col min="13" max="15" width="20.84765625" customWidth="1"/>
+    <col min="16" max="16" width="21.5234375" customWidth="1"/>
+    <col min="17" max="17" width="29.19140625" customWidth="1"/>
+    <col min="18" max="18" width="25.828125" customWidth="1"/>
+    <col min="19" max="19" width="32.8203125" customWidth="1"/>
+    <col min="20" max="21" width="20.84765625" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="23" max="23" width="25.01953125" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" customWidth="1"/>
+    <col min="25" max="25" width="20.84765625" customWidth="1"/>
+    <col min="26" max="26" width="14.796875" customWidth="1"/>
+    <col min="27" max="27" width="15.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="35"/>
       <c r="D1" s="42" t="s">
         <v>32</v>
@@ -13621,7 +13547,7 @@
       <c r="Z1" s="45"/>
       <c r="AA1" s="45"/>
     </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -13704,7 +13630,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="38.25">
+    <row r="3" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -13775,7 +13701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.5">
+    <row r="4" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -13846,7 +13772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.5">
+    <row r="5" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -13917,7 +13843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.5">
+    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -13988,7 +13914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.5">
+    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14059,7 +13985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.5">
+    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14130,7 +14056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.5">
+    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14201,7 +14127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.5">
+    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14272,8 +14198,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1"/>
-    <row r="12" spans="1:27" ht="38.25">
+    <row r="11" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14344,7 +14270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.5">
+    <row r="13" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14415,7 +14341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.5">
+    <row r="14" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14486,7 +14412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.5">
+    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14557,7 +14483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.5">
+    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14628,7 +14554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.5">
+    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -14699,7 +14625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.5">
+    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -14770,7 +14696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.5">
+    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -14841,8 +14767,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1"/>
-    <row r="21" spans="1:27" ht="38.25">
+    <row r="20" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -14913,7 +14839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.5">
+    <row r="22" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -14984,7 +14910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.5">
+    <row r="23" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15055,7 +14981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.5">
+    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15126,7 +15052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.5">
+    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15197,7 +15123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.5">
+    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15268,7 +15194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.5">
+    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15339,7 +15265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.5">
+    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15410,7 +15336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.5">
+    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15481,8 +15407,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1"/>
-    <row r="31" spans="1:27" ht="19.5">
+    <row r="30" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -15553,7 +15479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.5">
+    <row r="32" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15624,7 +15550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.5">
+    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -15695,7 +15621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.5">
+    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -15766,7 +15692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="38.25">
+    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -15837,7 +15763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.5">
+    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -15908,7 +15834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.5">
+    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -15979,7 +15905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.5">
+    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -16050,7 +15976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.5">
+    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16121,7 +16047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.5">
+    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16192,7 +16118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.5">
+    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16263,8 +16189,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.5">
+    <row r="42" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16335,7 +16261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.5">
+    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16406,7 +16332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.5">
+    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16477,7 +16403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.5">
+    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16548,7 +16474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="38.25">
+    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16619,7 +16545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.5">
+    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -16690,7 +16616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.5">
+    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -16761,7 +16687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.5">
+    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -16832,7 +16758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.5">
+    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -16903,7 +16829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.5">
+    <row r="52" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -16974,7 +16900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.5">
+    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -17045,8 +16971,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.5">
+    <row r="54" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17117,7 +17043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.5">
+    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17188,7 +17114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.5">
+    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17259,7 +17185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.5">
+    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17330,7 +17256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="38.25">
+    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17401,7 +17327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.5">
+    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17472,7 +17398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.5">
+    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -17543,7 +17469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.5">
+    <row r="62" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -17614,7 +17540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.5">
+    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -17685,7 +17611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.5">
+    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -17756,7 +17682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.5">
+    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -17827,8 +17753,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -17897,7 +17823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -17966,7 +17892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -18035,7 +17961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18104,7 +18030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18173,7 +18099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18242,7 +18168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18311,7 +18237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18380,7 +18306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18449,7 +18375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -18518,7 +18444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -18587,8 +18513,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -18657,7 +18583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -18726,7 +18652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -18795,7 +18721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -18864,7 +18790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -18933,7 +18859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -19002,7 +18928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -19071,7 +18997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19140,7 +19066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19209,7 +19135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19278,7 +19204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19347,8 +19273,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19417,7 +19343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999">
+    <row r="92" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19486,7 +19412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19555,7 +19481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -19624,7 +19550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -19693,7 +19619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -19762,7 +19688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -19831,7 +19757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -19900,7 +19826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -19969,7 +19895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -20038,7 +19964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -20107,8 +20033,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="103" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20177,7 +20103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20246,7 +20172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20315,7 +20241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20384,7 +20310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999">
+    <row r="107" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20453,7 +20379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20522,7 +20448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999">
+    <row r="109" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -20591,7 +20517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999">
+    <row r="110" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -20660,7 +20586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
+    <row r="111" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -20729,7 +20655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -20798,7 +20724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.149999999999999">
+    <row r="113" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -20867,8 +20793,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="7" customFormat="1"/>
-    <row r="115" spans="1:28" ht="38.450000000000003">
+    <row r="114" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="115" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>23</v>
       </c>
@@ -20937,7 +20863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
+    <row r="116" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>23</v>
       </c>
@@ -21006,7 +20932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>23</v>
       </c>
@@ -21075,7 +21001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
+    <row r="118" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>23</v>
       </c>
@@ -21144,7 +21070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>23</v>
       </c>
@@ -21213,7 +21139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
+    <row r="120" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>23</v>
       </c>
@@ -21282,7 +21208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>23</v>
       </c>
@@ -21351,7 +21277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>23</v>
       </c>
@@ -21420,8 +21346,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28" s="7" customFormat="1"/>
-    <row r="124" spans="1:28">
+    <row r="123" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -21451,7 +21377,7 @@
       <c r="AA124" s="7"/>
       <c r="AB124" s="7"/>
     </row>
-    <row r="125" spans="1:28">
+    <row r="125" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -21481,7 +21407,7 @@
       <c r="AA125" s="7"/>
       <c r="AB125" s="7"/>
     </row>
-    <row r="126" spans="1:28">
+    <row r="126" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -21511,7 +21437,7 @@
       <c r="AA126" s="7"/>
       <c r="AB126" s="7"/>
     </row>
-    <row r="127" spans="1:28">
+    <row r="127" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -21541,7 +21467,7 @@
       <c r="AA127" s="7"/>
       <c r="AB127" s="7"/>
     </row>
-    <row r="128" spans="1:28">
+    <row r="128" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -21571,7 +21497,7 @@
       <c r="AA128" s="7"/>
       <c r="AB128" s="7"/>
     </row>
-    <row r="129" spans="1:28">
+    <row r="129" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -21601,7 +21527,7 @@
       <c r="AA129" s="7"/>
       <c r="AB129" s="7"/>
     </row>
-    <row r="130" spans="1:28">
+    <row r="130" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -21631,7 +21557,7 @@
       <c r="AA130" s="7"/>
       <c r="AB130" s="7"/>
     </row>
-    <row r="131" spans="1:28">
+    <row r="131" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -21661,7 +21587,7 @@
       <c r="AA131" s="7"/>
       <c r="AB131" s="7"/>
     </row>
-    <row r="132" spans="1:28">
+    <row r="132" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -21691,7 +21617,7 @@
       <c r="AA132" s="7"/>
       <c r="AB132" s="7"/>
     </row>
-    <row r="133" spans="1:28">
+    <row r="133" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -21721,7 +21647,7 @@
       <c r="AA133" s="7"/>
       <c r="AB133" s="7"/>
     </row>
-    <row r="134" spans="1:28">
+    <row r="134" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -21751,7 +21677,7 @@
       <c r="AA134" s="7"/>
       <c r="AB134" s="7"/>
     </row>
-    <row r="135" spans="1:28">
+    <row r="135" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -21781,7 +21707,7 @@
       <c r="AA135" s="7"/>
       <c r="AB135" s="7"/>
     </row>
-    <row r="136" spans="1:28">
+    <row r="136" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -21811,7 +21737,7 @@
       <c r="AA136" s="7"/>
       <c r="AB136" s="7"/>
     </row>
-    <row r="137" spans="1:28">
+    <row r="137" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -21841,7 +21767,7 @@
       <c r="AA137" s="7"/>
       <c r="AB137" s="7"/>
     </row>
-    <row r="138" spans="1:28">
+    <row r="138" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -21871,7 +21797,7 @@
       <c r="AA138" s="7"/>
       <c r="AB138" s="7"/>
     </row>
-    <row r="139" spans="1:28">
+    <row r="139" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
@@ -21901,7 +21827,7 @@
       <c r="AA139" s="7"/>
       <c r="AB139" s="7"/>
     </row>
-    <row r="140" spans="1:28">
+    <row r="140" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
@@ -21931,186 +21857,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22128,8 +21874,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R3:R8 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10" xr:uid="{9601545B-0042-44B0-BF74-48AB1C0F51DD}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel-files/QUEZON CITY/SAN ANTONIO ES.xlsx
+++ b/excel-files/QUEZON CITY/SAN ANTONIO ES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10320"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10403"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DD6C8A3-06F6-FB42-8EA5-FEEF5F1B112D}"/>
+  <xr:revisionPtr revIDLastSave="228" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F52D436E-5874-CF45-BF5E-ED225E033B29}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -308,6 +308,12 @@
   </si>
   <si>
     <t>Arts</t>
+  </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>RO</t>
   </si>
 </sst>
 </file>
@@ -1729,10 +1735,8 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
@@ -1742,8 +1746,6 @@
         <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1770,7 +1772,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
@@ -1780,56 +1782,6 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
@@ -1859,19 +1811,17 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
         <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
       </border>
     </dxf>
     <dxf>
@@ -1892,20 +1842,26 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <sz val="15"/>
+        <color rgb="FF000000"/>
         <name val="Bookman Old Style"/>
-        <family val="1"/>
         <charset val="134"/>
         <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="-0.499984740745262"/>
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFCAEDFB"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2877,8 +2833,10 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
@@ -2888,6 +2846,8 @@
         <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2914,7 +2874,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
@@ -2924,6 +2884,56 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
@@ -2953,17 +2963,19 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
           <color rgb="FF000000"/>
-        </left>
-        <right/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2984,26 +2996,20 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color rgb="FF000000"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
         <name val="Bookman Old Style"/>
+        <family val="1"/>
         <charset val="134"/>
         <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFCAEDFB"/>
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -3019,7 +3025,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="32" headerRowBorderDxfId="31" tableBorderDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="61" tableBorderDxfId="60">
   <autoFilter ref="A1:H145" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
@@ -3036,54 +3042,54 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
   <autoFilter ref="A2:AA127" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{C6CCCB1C-6639-4C28-A4BA-B187B2F73B59}" name="SUBJECTS" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{945324E6-140A-476C-A8C3-23A16D4D262F}" name="Enrolment S.Y. 2025-2026 " dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{A2D4C0AF-3699-4D3C-A791-2D7D8004CC89}" name="Quantity based on Target LAS - Q1 " dataDxfId="23">
+    <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{C6CCCB1C-6639-4C28-A4BA-B187B2F73B59}" name="SUBJECTS" dataDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{945324E6-140A-476C-A8C3-23A16D4D262F}" name="Enrolment S.Y. 2025-2026 " dataDxfId="54"/>
+    <tableColumn id="4" xr3:uid="{A2D4C0AF-3699-4D3C-A791-2D7D8004CC89}" name="Quantity based on Target LAS - Q1 " dataDxfId="53">
       <calculatedColumnFormula>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9CE2D7B1-8761-49A3-A313-E7834B16687D}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q1" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{FCD520AB-D938-4542-9B56-AEC07AB5F1DC}" name="Year of Delivery-LAS - Q1" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{674474DE-9D20-41C1-8261-DA9C4A95671C}" name="SOURCE - LAS (CO,RO, SDO) - Q1" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{58D9CB98-8F6F-4F61-9103-C27B8FFBDB51}" name="GAP - LAS - Q1" dataDxfId="19">
+    <tableColumn id="5" xr3:uid="{9CE2D7B1-8761-49A3-A313-E7834B16687D}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q1" dataDxfId="52"/>
+    <tableColumn id="6" xr3:uid="{FCD520AB-D938-4542-9B56-AEC07AB5F1DC}" name="Year of Delivery-LAS - Q1" dataDxfId="51"/>
+    <tableColumn id="7" xr3:uid="{674474DE-9D20-41C1-8261-DA9C4A95671C}" name="SOURCE - LAS (CO,RO, SDO) - Q1" dataDxfId="50"/>
+    <tableColumn id="8" xr3:uid="{58D9CB98-8F6F-4F61-9103-C27B8FFBDB51}" name="GAP - LAS - Q1" dataDxfId="49">
       <calculatedColumnFormula>IF((D3-E3)&lt;0,0,(D3-E3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E6406FC4-4491-4FD6-9EA2-F088E94C44F4}" name="SURPLUS - LAS - Q1" dataDxfId="18">
+    <tableColumn id="9" xr3:uid="{E6406FC4-4491-4FD6-9EA2-F088E94C44F4}" name="SURPLUS - LAS - Q1" dataDxfId="48">
       <calculatedColumnFormula>IF((E3-D3)&lt;0,0,(E3-D3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1E56D889-DC27-4BCB-B61E-06BBBE734949}" name="Quantity based on Target LAS - Q2" dataDxfId="17">
+    <tableColumn id="10" xr3:uid="{1E56D889-DC27-4BCB-B61E-06BBBE734949}" name="Quantity based on Target LAS - Q2" dataDxfId="47">
       <calculatedColumnFormula>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{E933BF99-834C-4F15-8181-7D005013BD85}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) Q2" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{F2E2CB95-E0BD-4C6E-ACFE-F201177004A0}" name="Year of Delivery-LAS Q2" dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{163FBFFB-0AB7-44C8-89C4-72AA64C1EAC7}" name="SOURCE-LAS (CO,RO, SDO) Q2" dataDxfId="14"/>
-    <tableColumn id="14" xr3:uid="{EACC05A8-C68D-4495-BC08-73F093C4992F}" name="GAP - LAS -Q2" dataDxfId="13"/>
-    <tableColumn id="15" xr3:uid="{28A44E24-3E28-4B7F-BADE-28BB84F0B810}" name="SURPLUS - LAS -Q2" dataDxfId="12"/>
-    <tableColumn id="16" xr3:uid="{87878677-5715-46B6-9BA9-9D08DE9A3335}" name="Quantity based on Target LAS - Q3" dataDxfId="11">
+    <tableColumn id="11" xr3:uid="{E933BF99-834C-4F15-8181-7D005013BD85}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) Q2" dataDxfId="46"/>
+    <tableColumn id="12" xr3:uid="{F2E2CB95-E0BD-4C6E-ACFE-F201177004A0}" name="Year of Delivery-LAS Q2" dataDxfId="45"/>
+    <tableColumn id="13" xr3:uid="{163FBFFB-0AB7-44C8-89C4-72AA64C1EAC7}" name="SOURCE-LAS (CO,RO, SDO) Q2" dataDxfId="44"/>
+    <tableColumn id="14" xr3:uid="{EACC05A8-C68D-4495-BC08-73F093C4992F}" name="GAP - LAS -Q2" dataDxfId="43"/>
+    <tableColumn id="15" xr3:uid="{28A44E24-3E28-4B7F-BADE-28BB84F0B810}" name="SURPLUS - LAS -Q2" dataDxfId="42"/>
+    <tableColumn id="16" xr3:uid="{87878677-5715-46B6-9BA9-9D08DE9A3335}" name="Quantity based on Target LAS - Q3" dataDxfId="41">
       <calculatedColumnFormula>#REF!*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{48667A1F-77B1-47A6-83F7-61ED15F61DDB}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q3" dataDxfId="10"/>
-    <tableColumn id="18" xr3:uid="{56F2625D-2CEE-478E-A8DE-42A7191C3835}" name="Year of Delivery-LAS - Q3" dataDxfId="9"/>
-    <tableColumn id="19" xr3:uid="{EF0F614F-5FED-4639-8798-840D9677B8DA}" name="SOURCE-LAS (CO,RO, SDO) - Q3" dataDxfId="8"/>
-    <tableColumn id="20" xr3:uid="{FD91DDEE-DBA8-4E2C-94B2-23AE9F73CC4A}" name="GAP - LAS - Q3" dataDxfId="7">
+    <tableColumn id="17" xr3:uid="{48667A1F-77B1-47A6-83F7-61ED15F61DDB}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q3" dataDxfId="40"/>
+    <tableColumn id="18" xr3:uid="{56F2625D-2CEE-478E-A8DE-42A7191C3835}" name="Year of Delivery-LAS - Q3" dataDxfId="39"/>
+    <tableColumn id="19" xr3:uid="{EF0F614F-5FED-4639-8798-840D9677B8DA}" name="SOURCE-LAS (CO,RO, SDO) - Q3" dataDxfId="38"/>
+    <tableColumn id="20" xr3:uid="{FD91DDEE-DBA8-4E2C-94B2-23AE9F73CC4A}" name="GAP - LAS - Q3" dataDxfId="37">
       <calculatedColumnFormula>IF((P3-Q3)&lt;0,0,(P3-Q3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{DB598C6C-E489-4B0F-9BC6-B0981F7D2582}" name="SURPLUS - LAS - Q3" dataDxfId="6">
+    <tableColumn id="21" xr3:uid="{DB598C6C-E489-4B0F-9BC6-B0981F7D2582}" name="SURPLUS - LAS - Q3" dataDxfId="36">
       <calculatedColumnFormula>IF((Q3-P3)&lt;0,0,(Q3-P3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{8CD6906A-7980-46E8-80B2-8563AEBC71F7}" name="Quantity based on Target LAS - Q4" dataDxfId="5">
+    <tableColumn id="22" xr3:uid="{8CD6906A-7980-46E8-80B2-8563AEBC71F7}" name="Quantity based on Target LAS - Q4" dataDxfId="35">
       <calculatedColumnFormula>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{6287B1E4-D2AD-47C7-BD86-3391F339B1E3}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS)- Q4" dataDxfId="4"/>
-    <tableColumn id="24" xr3:uid="{205BCDBA-0424-492C-B4EF-841B8A3A1521}" name="Year of Delivery - LAS - Q4" dataDxfId="3"/>
-    <tableColumn id="25" xr3:uid="{8226E35B-1F3B-4D2A-815B-9D4C0A24EE7E}" name="SOURCE - LAS (CO,RO, SDO) - Q4" dataDxfId="2"/>
-    <tableColumn id="26" xr3:uid="{5B37A4B7-CD16-4D9A-8A47-D9EA73F613BC}" name="GAP - LAS - Q4" dataDxfId="1">
+    <tableColumn id="23" xr3:uid="{6287B1E4-D2AD-47C7-BD86-3391F339B1E3}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS)- Q4" dataDxfId="34"/>
+    <tableColumn id="24" xr3:uid="{205BCDBA-0424-492C-B4EF-841B8A3A1521}" name="Year of Delivery - LAS - Q4" dataDxfId="33"/>
+    <tableColumn id="25" xr3:uid="{8226E35B-1F3B-4D2A-815B-9D4C0A24EE7E}" name="SOURCE - LAS (CO,RO, SDO) - Q4" dataDxfId="32"/>
+    <tableColumn id="26" xr3:uid="{5B37A4B7-CD16-4D9A-8A47-D9EA73F613BC}" name="GAP - LAS - Q4" dataDxfId="31">
       <calculatedColumnFormula>IF((V3-W3)&lt;0,0,(V3-W3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{38E9C5F3-3FF5-4B13-A9DA-0081A90F35C5}" name="SURPLUS - LAS - Q4" dataDxfId="0">
+    <tableColumn id="27" xr3:uid="{38E9C5F3-3FF5-4B13-A9DA-0081A90F35C5}" name="SURPLUS - LAS - Q4" dataDxfId="30">
       <calculatedColumnFormula>IF((W3-V3)&lt;0,0,(W3-V3))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3092,54 +3098,54 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="61" headerRowBorderDxfId="62" tableBorderDxfId="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
   <autoFilter ref="A2:AA140" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="59"/>
-    <tableColumn id="2" xr3:uid="{73AEA048-228E-40E8-B07A-3A7C30BA0DC7}" name="SUBJECTS" dataDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{187AF7E3-9651-4001-B779-AADEF0EAB05A}" name="Enrolment S.Y. 2025-2026 " dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{41F05D2B-5E6F-433A-B62B-2F1726EA10F2}" name="Quantity based on Target ADM-SLM - Q1 " dataDxfId="56">
+    <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{73AEA048-228E-40E8-B07A-3A7C30BA0DC7}" name="SUBJECTS" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{187AF7E3-9651-4001-B779-AADEF0EAB05A}" name="Enrolment S.Y. 2025-2026 " dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{41F05D2B-5E6F-433A-B62B-2F1726EA10F2}" name="Quantity based on Target ADM-SLM - Q1 " dataDxfId="23">
       <calculatedColumnFormula>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CDE5FD66-559D-4D0F-A587-312B6DC04A00}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q1" dataDxfId="55"/>
-    <tableColumn id="6" xr3:uid="{339CCB0D-A0D6-41EF-9023-6B8DF1A1D211}" name="Year of Delivery - ADM-SLM - Q1" dataDxfId="54"/>
-    <tableColumn id="7" xr3:uid="{66966C8F-6B7D-4027-80F0-10F5BEB94C36}" name="SOURCE - ADM-SLM (CO,RO, SDO) - Q1" dataDxfId="53"/>
-    <tableColumn id="8" xr3:uid="{F205DFF0-AD23-4608-82A0-E64C38A40A7F}" name="GAP - ADM-SLM - Q1" dataDxfId="52">
+    <tableColumn id="5" xr3:uid="{CDE5FD66-559D-4D0F-A587-312B6DC04A00}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q1" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{339CCB0D-A0D6-41EF-9023-6B8DF1A1D211}" name="Year of Delivery - ADM-SLM - Q1" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{66966C8F-6B7D-4027-80F0-10F5BEB94C36}" name="SOURCE - ADM-SLM (CO,RO, SDO) - Q1" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{F205DFF0-AD23-4608-82A0-E64C38A40A7F}" name="GAP - ADM-SLM - Q1" dataDxfId="19">
       <calculatedColumnFormula>IF((D3-E3)&lt;0,0,(D3-E3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{A97DBFEB-A833-47C5-A43D-C6E4D77683A6}" name="SURPLUS - ADM-SLM - Q1" dataDxfId="51">
+    <tableColumn id="9" xr3:uid="{A97DBFEB-A833-47C5-A43D-C6E4D77683A6}" name="SURPLUS - ADM-SLM - Q1" dataDxfId="18">
       <calculatedColumnFormula>IF((E3-D3)&lt;0,0,(E3-D3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{6A093D68-BC9F-46BB-AC8F-CA208309466C}" name="Quantity based on Target ADM-SLM - Q2" dataDxfId="50">
+    <tableColumn id="10" xr3:uid="{6A093D68-BC9F-46BB-AC8F-CA208309466C}" name="Quantity based on Target ADM-SLM - Q2" dataDxfId="17">
       <calculatedColumnFormula>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{CB914A26-115B-4765-A39C-5A2824E73671}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q2" dataDxfId="49"/>
-    <tableColumn id="12" xr3:uid="{35FFB32F-868E-4FBD-946A-0482CC3DE0D4}" name="Year of Delivery - ADM-SLM Q2" dataDxfId="48"/>
-    <tableColumn id="13" xr3:uid="{987FB8ED-06DA-4311-80C5-DAF78B602129}" name="SOURCE - ADM-SLM (CO,RO, SDO) Q2" dataDxfId="47"/>
-    <tableColumn id="14" xr3:uid="{24CC35CF-2900-4C84-934F-7E29CCFCCEC9}" name="GAP - ADM-SLM - Q2" dataDxfId="46"/>
-    <tableColumn id="15" xr3:uid="{0DA82B8D-6A8D-469A-8302-7E7DD0B1BDC4}" name="SURPLUS - ADM-SLM -Q2" dataDxfId="45"/>
-    <tableColumn id="16" xr3:uid="{126A7F40-0CC3-4264-A57D-D7C0C9FE4720}" name="Quantity based on Target ADM-SLM - Q3" dataDxfId="44">
+    <tableColumn id="11" xr3:uid="{CB914A26-115B-4765-A39C-5A2824E73671}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q2" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{35FFB32F-868E-4FBD-946A-0482CC3DE0D4}" name="Year of Delivery - ADM-SLM Q2" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{987FB8ED-06DA-4311-80C5-DAF78B602129}" name="SOURCE - ADM-SLM (CO,RO, SDO) Q2" dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{24CC35CF-2900-4C84-934F-7E29CCFCCEC9}" name="GAP - ADM-SLM - Q2" dataDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{0DA82B8D-6A8D-469A-8302-7E7DD0B1BDC4}" name="SURPLUS - ADM-SLM -Q2" dataDxfId="12"/>
+    <tableColumn id="16" xr3:uid="{126A7F40-0CC3-4264-A57D-D7C0C9FE4720}" name="Quantity based on Target ADM-SLM - Q3" dataDxfId="11">
       <calculatedColumnFormula>#REF!*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{711B70A4-2160-43C1-900D-FD892755D7AB}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q3" dataDxfId="43"/>
-    <tableColumn id="18" xr3:uid="{D8C99A72-7FED-4E85-8CB4-4A08C56BCB15}" name="Year of Delivery - ADM-SLM - Q3" dataDxfId="42"/>
-    <tableColumn id="19" xr3:uid="{D48A881D-138B-4288-AA57-050C0AE3F5F6}" name="SOURCE - ADM-SLM(CO,RO, SDO) - Q3" dataDxfId="41"/>
-    <tableColumn id="20" xr3:uid="{B03A44EC-B25E-4D0D-B9E6-71825AC6E51F}" name="GAP - ADM-SLM - Q3" dataDxfId="40">
+    <tableColumn id="17" xr3:uid="{711B70A4-2160-43C1-900D-FD892755D7AB}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q3" dataDxfId="10"/>
+    <tableColumn id="18" xr3:uid="{D8C99A72-7FED-4E85-8CB4-4A08C56BCB15}" name="Year of Delivery - ADM-SLM - Q3" dataDxfId="9"/>
+    <tableColumn id="19" xr3:uid="{D48A881D-138B-4288-AA57-050C0AE3F5F6}" name="SOURCE - ADM-SLM(CO,RO, SDO) - Q3" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{B03A44EC-B25E-4D0D-B9E6-71825AC6E51F}" name="GAP - ADM-SLM - Q3" dataDxfId="7">
       <calculatedColumnFormula>IF((P3-Q3)&lt;0,0,(P3-Q3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{3338E724-88DC-45DA-8F55-7AAE5A560621}" name="SURPLUS - ADM-SLM - Q3" dataDxfId="39">
+    <tableColumn id="21" xr3:uid="{3338E724-88DC-45DA-8F55-7AAE5A560621}" name="SURPLUS - ADM-SLM - Q3" dataDxfId="6">
       <calculatedColumnFormula>IF((Q3-P3)&lt;0,0,(Q3-P3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{AC55FA3C-A61A-4AB0-8391-EC237845F1BF}" name="Quantity based on Target ADM-SLM - Q4" dataDxfId="38">
+    <tableColumn id="22" xr3:uid="{AC55FA3C-A61A-4AB0-8391-EC237845F1BF}" name="Quantity based on Target ADM-SLM - Q4" dataDxfId="5">
       <calculatedColumnFormula>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{D3F77FA4-2477-4BAF-A6FD-8446908907B9}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM)- Q4" dataDxfId="37"/>
-    <tableColumn id="24" xr3:uid="{C66CE0BE-6DCF-4E05-9DBD-D908450B3841}" name="Year of Delivery - ADM-SLM- Q4" dataDxfId="36"/>
-    <tableColumn id="25" xr3:uid="{AABA2263-B244-4CBF-87B1-CDAAECF763E4}" name="SOURCE - ADM-SLM - (CO,RO, SDO) - Q4" dataDxfId="35"/>
-    <tableColumn id="26" xr3:uid="{21E1F5D8-F09B-453A-90E6-AA7B2E8821D1}" name="GAP - ADM-SLM - Q4" dataDxfId="34">
+    <tableColumn id="23" xr3:uid="{D3F77FA4-2477-4BAF-A6FD-8446908907B9}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM)- Q4" dataDxfId="4"/>
+    <tableColumn id="24" xr3:uid="{C66CE0BE-6DCF-4E05-9DBD-D908450B3841}" name="Year of Delivery - ADM-SLM- Q4" dataDxfId="3"/>
+    <tableColumn id="25" xr3:uid="{AABA2263-B244-4CBF-87B1-CDAAECF763E4}" name="SOURCE - ADM-SLM - (CO,RO, SDO) - Q4" dataDxfId="2"/>
+    <tableColumn id="26" xr3:uid="{21E1F5D8-F09B-453A-90E6-AA7B2E8821D1}" name="GAP - ADM-SLM - Q4" dataDxfId="1">
       <calculatedColumnFormula>IF((V3-W3)&lt;0,0,(V3-W3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{67725D86-C1DE-4DB2-8FBD-99B8821906AB}" name="SURPLUS - ADM-SLM- Q4" dataDxfId="33">
+    <tableColumn id="27" xr3:uid="{67725D86-C1DE-4DB2-8FBD-99B8821906AB}" name="SURPLUS - ADM-SLM- Q4" dataDxfId="0">
       <calculatedColumnFormula>IF((W3-V3)&lt;0,0,(W3-V3))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3508,17 +3514,25 @@
       <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="5"/>
+      <c r="C2" s="1">
+        <v>317</v>
+      </c>
+      <c r="D2" s="1">
+        <v>473</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G2" s="3">
         <f>IF((C2-D2)&lt;0,0,C2-D2)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
         <f>IF((D2-C2)&lt;0,0,D2-C2)</f>
-        <v>0</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3528,17 +3542,25 @@
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="5"/>
+      <c r="C3" s="1">
+        <v>317</v>
+      </c>
+      <c r="D3" s="1">
+        <v>473</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G3" s="3">
         <f>IF((C3-D3)&lt;0,0,C3-D3)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
         <f>IF((D3-C3)&lt;0,0,D3-C3)</f>
-        <v>0</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -3548,17 +3570,25 @@
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="5"/>
+      <c r="C4" s="1">
+        <v>317</v>
+      </c>
+      <c r="D4" s="1">
+        <v>473</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G4" s="3">
         <f>IF((C4-D4)&lt;0,0,C4-D4)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
         <f>IF((D4-C4)&lt;0,0,D4-C4)</f>
-        <v>0</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3568,17 +3598,25 @@
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="5"/>
+      <c r="C5" s="1">
+        <v>317</v>
+      </c>
+      <c r="D5" s="1">
+        <v>473</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G5" s="3">
         <f t="shared" ref="G5:G6" si="0">IF((C5-D5)&lt;0,0,C5-D5)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" ref="H5:H6" si="1">IF((D5-C5)&lt;0,0,D5-C5)</f>
-        <v>0</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
@@ -3588,13 +3626,15 @@
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="1">
+        <v>317</v>
+      </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="5"/>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>317</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="1"/>
@@ -3613,13 +3653,15 @@
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="1">
+        <v>348</v>
+      </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="5"/>
       <c r="G8" s="3">
         <f>IF((C8-D8)&lt;0,0,C8-D8)</f>
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="H8" s="4">
         <f>IF((D8-C8)&lt;0,0,D8-C8)</f>
@@ -3633,13 +3675,15 @@
       <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="1"/>
+      <c r="C9" s="1">
+        <v>348</v>
+      </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="5"/>
       <c r="G9" s="3">
         <f>IF((C9-D9)&lt;0,0,C9-D9)</f>
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="H9" s="4">
         <f>IF((D9-C9)&lt;0,0,D9-C9)</f>
@@ -3653,13 +3697,15 @@
       <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1">
+        <v>348</v>
+      </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="5"/>
       <c r="G10" s="3">
         <f>IF((C10-D10)&lt;0,0,C10-D10)</f>
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="H10" s="4">
         <f>IF((D10-C10)&lt;0,0,D10-C10)</f>
@@ -3673,17 +3719,25 @@
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+      <c r="C11" s="1">
+        <v>348</v>
+      </c>
+      <c r="D11" s="1">
+        <v>430</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
-        <v>0</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
@@ -3693,13 +3747,15 @@
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="1">
+        <v>348</v>
+      </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="5"/>
       <c r="G12" s="3">
         <f>IF((C12-D12)&lt;0,0,C12-D12)</f>
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="H12" s="4">
         <f>IF((D12-C12)&lt;0,0,D12-C12)</f>
@@ -3718,13 +3774,15 @@
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="1"/>
+      <c r="C14" s="1">
+        <v>378</v>
+      </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="5"/>
       <c r="G14" s="3">
         <f t="shared" ref="G14:G19" si="2">IF((C14-D14)&lt;0,0,C14-D14)</f>
-        <v>0</v>
+        <v>378</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" ref="H14:H19" si="3">IF((D14-C14)&lt;0,0,D14-C14)</f>
@@ -3738,13 +3796,15 @@
       <c r="B15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="1"/>
+      <c r="C15" s="1">
+        <v>378</v>
+      </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="5"/>
       <c r="G15" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>378</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="3"/>
@@ -3758,13 +3818,15 @@
       <c r="B16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="1"/>
+      <c r="C16" s="1">
+        <v>378</v>
+      </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="5"/>
       <c r="G16" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>378</v>
       </c>
       <c r="H16" s="4">
         <f t="shared" si="3"/>
@@ -3778,13 +3840,15 @@
       <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="1"/>
+      <c r="C17" s="1">
+        <v>378</v>
+      </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="5"/>
       <c r="G17" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>378</v>
       </c>
       <c r="H17" s="4">
         <f t="shared" si="3"/>
@@ -3798,13 +3862,15 @@
       <c r="B18" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="1"/>
+      <c r="C18" s="1">
+        <v>378</v>
+      </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="5"/>
       <c r="G18" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>378</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="3"/>
@@ -3818,13 +3884,15 @@
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="1"/>
+      <c r="C19" s="1">
+        <v>378</v>
+      </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="5"/>
       <c r="G19" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>378</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="3"/>
@@ -3848,13 +3916,15 @@
       <c r="B21" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="1"/>
+      <c r="C21" s="1">
+        <v>429</v>
+      </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="5"/>
       <c r="G21" s="3">
         <f t="shared" ref="G21:G29" si="4">IF((C21-D21)&lt;0,0,C21-D21)</f>
-        <v>0</v>
+        <v>429</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" ref="H21:H29" si="5">IF((D21-C21)&lt;0,0,D21-C21)</f>
@@ -3868,37 +3938,53 @@
       <c r="B22" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="5"/>
+      <c r="C22" s="1">
+        <v>429</v>
+      </c>
+      <c r="D22" s="1">
+        <v>440</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>4</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="5"/>
+      <c r="C23" s="1">
+        <v>429</v>
+      </c>
+      <c r="D23" s="1">
+        <v>440</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G23" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -3908,17 +3994,25 @@
       <c r="B24" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="5"/>
+      <c r="C24" s="1">
+        <v>429</v>
+      </c>
+      <c r="D24" s="1">
+        <v>440</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G24" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3928,17 +4022,25 @@
       <c r="B25" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="5"/>
+      <c r="C25" s="1">
+        <v>429</v>
+      </c>
+      <c r="D25" s="1">
+        <v>440</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G25" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3948,17 +4050,25 @@
       <c r="B26" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="5"/>
+      <c r="C26" s="1">
+        <v>429</v>
+      </c>
+      <c r="D26" s="1">
+        <v>440</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G26" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H26" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3968,17 +4078,25 @@
       <c r="B27" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="5"/>
+      <c r="C27" s="1">
+        <v>429</v>
+      </c>
+      <c r="D27" s="1">
+        <v>440</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G27" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H27" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3988,13 +4106,15 @@
       <c r="B28" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="1"/>
+      <c r="C28" s="1">
+        <v>429</v>
+      </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="5"/>
       <c r="G28" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>429</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="5"/>
@@ -4008,17 +4128,25 @@
       <c r="B29" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+      <c r="C29" s="1">
+        <v>429</v>
+      </c>
+      <c r="D29" s="1">
+        <v>440</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4038,17 +4166,25 @@
       <c r="B31" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="5"/>
+      <c r="C31" s="1">
+        <v>312</v>
+      </c>
+      <c r="D31" s="1">
+        <v>460</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
         <v>0</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>0</v>
+        <v>148</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4058,13 +4194,15 @@
       <c r="B32" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="1"/>
+      <c r="C32" s="1">
+        <v>312</v>
+      </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="5"/>
       <c r="G32" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="7"/>
@@ -4078,13 +4216,15 @@
       <c r="B33" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C33" s="1"/>
+      <c r="C33" s="1">
+        <v>312</v>
+      </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="5"/>
       <c r="G33" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="7"/>
@@ -4098,13 +4238,15 @@
       <c r="B34" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="1"/>
+      <c r="C34" s="1">
+        <v>312</v>
+      </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="5"/>
       <c r="G34" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="7"/>
@@ -4118,17 +4260,25 @@
       <c r="B35" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="5"/>
+      <c r="C35" s="1">
+        <v>312</v>
+      </c>
+      <c r="D35" s="1">
+        <v>460</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4138,17 +4288,25 @@
       <c r="B36" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="5"/>
+      <c r="C36" s="1">
+        <v>312</v>
+      </c>
+      <c r="D36" s="1">
+        <v>460</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4158,17 +4316,25 @@
       <c r="B37" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="5"/>
+      <c r="C37" s="1">
+        <v>312</v>
+      </c>
+      <c r="D37" s="1">
+        <v>460</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4178,17 +4344,25 @@
       <c r="B38" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+      <c r="C38" s="1">
+        <v>312</v>
+      </c>
+      <c r="D38" s="1">
+        <v>460</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>148</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4198,13 +4372,15 @@
       <c r="B39" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="1"/>
+      <c r="C39" s="1">
+        <v>312</v>
+      </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="5"/>
       <c r="G39" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="7"/>
@@ -4228,13 +4404,15 @@
       <c r="B41" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C41" s="1"/>
+      <c r="C41" s="1">
+        <v>344</v>
+      </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="5"/>
       <c r="G41" s="3">
         <f t="shared" ref="G41:G49" si="8">IF((C41-D41)&lt;0,0,C41-D41)</f>
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="H41" s="4">
         <f t="shared" ref="H41:H49" si="9">IF((D41-C41)&lt;0,0,D41-C41)</f>
@@ -4248,13 +4426,15 @@
       <c r="B42" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C42" s="1"/>
+      <c r="C42" s="1">
+        <v>344</v>
+      </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="5"/>
       <c r="G42" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="H42" s="4">
         <f t="shared" si="9"/>
@@ -4268,13 +4448,15 @@
       <c r="B43" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C43" s="1"/>
+      <c r="C43" s="1">
+        <v>344</v>
+      </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="5"/>
       <c r="G43" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="H43" s="4">
         <f t="shared" si="9"/>
@@ -4288,13 +4470,15 @@
       <c r="B44" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C44" s="1"/>
+      <c r="C44" s="1">
+        <v>344</v>
+      </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="5"/>
       <c r="G44" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" si="9"/>
@@ -4308,13 +4492,15 @@
       <c r="B45" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="1"/>
+      <c r="C45" s="1">
+        <v>344</v>
+      </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="5"/>
       <c r="G45" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="H45" s="4">
         <f t="shared" si="9"/>
@@ -4328,13 +4514,15 @@
       <c r="B46" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C46" s="1"/>
+      <c r="C46" s="1">
+        <v>344</v>
+      </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="5"/>
       <c r="G46" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="H46" s="4">
         <f t="shared" si="9"/>
@@ -4348,13 +4536,15 @@
       <c r="B47" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="1"/>
+      <c r="C47" s="1">
+        <v>344</v>
+      </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="5"/>
       <c r="G47" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="H47" s="4">
         <f t="shared" si="9"/>
@@ -4368,13 +4558,15 @@
       <c r="B48" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="1"/>
+      <c r="C48" s="1">
+        <v>344</v>
+      </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="5"/>
       <c r="G48" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="H48" s="4">
         <f t="shared" si="9"/>
@@ -4388,13 +4580,15 @@
       <c r="B49" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C49" s="1"/>
+      <c r="C49" s="1">
+        <v>344</v>
+      </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="5"/>
       <c r="G49" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="H49" s="4">
         <f t="shared" si="9"/>
